--- a/Fundamental_Shortlist.xlsx
+++ b/Fundamental_Shortlist.xlsx
@@ -477,16 +477,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>187.65</v>
+        <v>187.35</v>
       </c>
       <c r="D2" t="n">
-        <v>361877.35</v>
+        <v>361298.8</v>
       </c>
       <c r="E2" t="n">
         <v>17.22</v>
       </c>
       <c r="F2" t="n">
-        <v>19.87</v>
+        <v>19.84</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -506,16 +506,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2849.4</v>
+        <v>2847</v>
       </c>
       <c r="D3" t="n">
-        <v>354331.12</v>
+        <v>354032.67</v>
       </c>
       <c r="E3" t="n">
         <v>15.1</v>
       </c>
       <c r="F3" t="n">
-        <v>18.5</v>
+        <v>18.49</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -535,16 +535,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>10289</v>
+        <v>10262.4</v>
       </c>
       <c r="D4" t="n">
-        <v>282745.72</v>
+        <v>282014.74</v>
       </c>
       <c r="E4" t="n">
         <v>28.24</v>
       </c>
       <c r="F4" t="n">
-        <v>23.95</v>
+        <v>23.88</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -564,16 +564,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>9454.5</v>
+        <v>9446</v>
       </c>
       <c r="D5" t="n">
-        <v>250987.27</v>
+        <v>250761.62</v>
       </c>
       <c r="E5" t="n">
         <v>21.97</v>
       </c>
       <c r="F5" t="n">
-        <v>84.3</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -593,16 +593,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1169.1</v>
+        <v>1164.8</v>
       </c>
       <c r="D6" t="n">
-        <v>225439.2</v>
+        <v>224610.02</v>
       </c>
       <c r="E6" t="n">
         <v>84.14</v>
       </c>
       <c r="F6" t="n">
-        <v>56.01</v>
+        <v>55.8</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -622,16 +622,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>498.5</v>
+        <v>497.95</v>
       </c>
       <c r="D7" t="n">
-        <v>210632.08</v>
+        <v>210399.69</v>
       </c>
       <c r="E7" t="n">
         <v>69.25</v>
       </c>
       <c r="F7" t="n">
-        <v>10.3</v>
+        <v>10.29</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -651,16 +651,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>7131.55</v>
+        <v>7121</v>
       </c>
       <c r="D8" t="n">
-        <v>195776.54</v>
+        <v>195486.92</v>
       </c>
       <c r="E8" t="n">
         <v>30.53</v>
       </c>
       <c r="F8" t="n">
-        <v>33.56</v>
+        <v>33.52</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -680,16 +680,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>4047.45</v>
+        <v>4047.35</v>
       </c>
       <c r="D9" t="n">
-        <v>192289.09</v>
+        <v>192284.34</v>
       </c>
       <c r="E9" t="n">
         <v>17.37</v>
       </c>
       <c r="F9" t="n">
-        <v>55.56</v>
+        <v>55.57</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -709,16 +709,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>18993</v>
+        <v>19004.8</v>
       </c>
       <c r="D10" t="n">
-        <v>171867.8</v>
+        <v>171974.58</v>
       </c>
       <c r="E10" t="n">
         <v>38.08</v>
       </c>
       <c r="F10" t="n">
-        <v>86.40000000000001</v>
+        <v>86.45</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -738,16 +738,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2804.2</v>
+        <v>2795.8</v>
       </c>
       <c r="D11" t="n">
-        <v>149529.04</v>
+        <v>149081.12</v>
       </c>
       <c r="E11" t="n">
         <v>28.34</v>
       </c>
       <c r="F11" t="n">
-        <v>81.81</v>
+        <v>81.56999999999999</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -767,16 +767,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>3446.2</v>
+        <v>3446.9</v>
       </c>
       <c r="D12" t="n">
-        <v>140565.01</v>
+        <v>140593.56</v>
       </c>
       <c r="E12" t="n">
         <v>59.99</v>
       </c>
       <c r="F12" t="n">
-        <v>49.62</v>
+        <v>49.63</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -796,16 +796,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2804.95</v>
+        <v>2802.5</v>
       </c>
       <c r="D13" t="n">
-        <v>138637.06</v>
+        <v>138515.97</v>
       </c>
       <c r="E13" t="n">
         <v>115.1</v>
       </c>
       <c r="F13" t="n">
-        <v>39.18</v>
+        <v>39.16</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -825,16 +825,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>831.3</v>
+        <v>831.6</v>
       </c>
       <c r="D14" t="n">
-        <v>130969.18</v>
+        <v>131016.42</v>
       </c>
       <c r="E14" t="n">
         <v>26.71</v>
       </c>
       <c r="F14" t="n">
-        <v>93.73999999999999</v>
+        <v>93.77</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -854,16 +854,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>28161.75</v>
+        <v>28076.8</v>
       </c>
       <c r="D15" t="n">
-        <v>125523.53</v>
+        <v>125144.89</v>
       </c>
       <c r="E15" t="n">
         <v>29.36</v>
       </c>
       <c r="F15" t="n">
-        <v>105.43</v>
+        <v>105.11</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -883,16 +883,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>187.4</v>
+        <v>187</v>
       </c>
       <c r="D16" t="n">
-        <v>117567.25</v>
+        <v>117316.32</v>
       </c>
       <c r="E16" t="n">
         <v>37.32</v>
       </c>
       <c r="F16" t="n">
-        <v>43.7</v>
+        <v>43.6</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -912,16 +912,16 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>7685.75</v>
+        <v>7680</v>
       </c>
       <c r="D17" t="n">
-        <v>115829.39</v>
+        <v>115742.74</v>
       </c>
       <c r="E17" t="n">
         <v>33.21</v>
       </c>
       <c r="F17" t="n">
-        <v>36.72</v>
+        <v>36.69</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -941,16 +941,16 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2130.9</v>
+        <v>2128.9</v>
       </c>
       <c r="D18" t="n">
-        <v>115135.04</v>
+        <v>115026.98</v>
       </c>
       <c r="E18" t="n">
         <v>17.76</v>
       </c>
       <c r="F18" t="n">
-        <v>105.33</v>
+        <v>105.23</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -970,16 +970,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>805.95</v>
+        <v>804.8</v>
       </c>
       <c r="D19" t="n">
-        <v>114721.53</v>
+        <v>114557.84</v>
       </c>
       <c r="E19" t="n">
         <v>17.06</v>
       </c>
       <c r="F19" t="n">
-        <v>57.06</v>
+        <v>56.98</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -999,10 +999,10 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>7891.45</v>
+        <v>7891.5</v>
       </c>
       <c r="D20" t="n">
-        <v>113466.94</v>
+        <v>113467.66</v>
       </c>
       <c r="E20" t="n">
         <v>17.45</v>
@@ -1028,16 +1028,16 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>4004.1</v>
+        <v>3995.95</v>
       </c>
       <c r="D21" t="n">
-        <v>102524.97</v>
+        <v>102316.28</v>
       </c>
       <c r="E21" t="n">
         <v>77.44</v>
       </c>
       <c r="F21" t="n">
-        <v>75.95</v>
+        <v>75.8</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1057,16 +1057,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1007.7</v>
+        <v>1003.2</v>
       </c>
       <c r="D22" t="n">
-        <v>100713.58</v>
+        <v>100263.84</v>
       </c>
       <c r="E22" t="n">
         <v>16.41</v>
       </c>
       <c r="F22" t="n">
-        <v>24.42</v>
+        <v>24.31</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1086,16 +1086,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1779.6</v>
+        <v>1773.85</v>
       </c>
       <c r="D23" t="n">
-        <v>100200.19</v>
+        <v>99876.42999999999</v>
       </c>
       <c r="E23" t="n">
         <v>27.29</v>
       </c>
       <c r="F23" t="n">
-        <v>21.08</v>
+        <v>21.01</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1115,16 +1115,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>2395.7</v>
+        <v>2395.2</v>
       </c>
       <c r="D24" t="n">
-        <v>96179.89</v>
+        <v>96159.83</v>
       </c>
       <c r="E24" t="n">
         <v>15.8</v>
       </c>
       <c r="F24" t="n">
-        <v>8.5</v>
+        <v>8.51</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1144,16 +1144,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>458.75</v>
+        <v>458.05</v>
       </c>
       <c r="D25" t="n">
-        <v>93439.48</v>
+        <v>93296.91</v>
       </c>
       <c r="E25" t="n">
         <v>56.5</v>
       </c>
       <c r="F25" t="n">
-        <v>30.89</v>
+        <v>30.84</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1173,16 +1173,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1951.6</v>
+        <v>1948.25</v>
       </c>
       <c r="D26" t="n">
-        <v>89245.33</v>
+        <v>89092.14</v>
       </c>
       <c r="E26" t="n">
         <v>29.93</v>
       </c>
       <c r="F26" t="n">
-        <v>14.97</v>
+        <v>14.95</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1202,16 +1202,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1976.3</v>
+        <v>1970.95</v>
       </c>
       <c r="D27" t="n">
-        <v>87557.77</v>
+        <v>87320.73</v>
       </c>
       <c r="E27" t="n">
         <v>23.5</v>
       </c>
       <c r="F27" t="n">
-        <v>40.36</v>
+        <v>40.26</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1231,16 +1231,16 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>9909</v>
+        <v>9899.4</v>
       </c>
       <c r="D28" t="n">
-        <v>86343.67999999999</v>
+        <v>86260.03</v>
       </c>
       <c r="E28" t="n">
         <v>45.28</v>
       </c>
       <c r="F28" t="n">
-        <v>24.19</v>
+        <v>24.16</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1260,10 +1260,10 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>3170</v>
+        <v>3169.8</v>
       </c>
       <c r="D29" t="n">
-        <v>80832.37</v>
+        <v>80827.28</v>
       </c>
       <c r="E29" t="n">
         <v>71.34999999999999</v>
@@ -1289,16 +1289,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>2281.9</v>
+        <v>2268.9</v>
       </c>
       <c r="D30" t="n">
-        <v>65639.11</v>
+        <v>65265.18</v>
       </c>
       <c r="E30" t="n">
         <v>38.45</v>
       </c>
       <c r="F30" t="n">
-        <v>16.3</v>
+        <v>16.2</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1318,16 +1318,16 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>2475</v>
+        <v>2465.25</v>
       </c>
       <c r="D31" t="n">
-        <v>65288.18</v>
+        <v>65030.98</v>
       </c>
       <c r="E31" t="n">
         <v>22.89</v>
       </c>
       <c r="F31" t="n">
-        <v>28.36</v>
+        <v>28.26</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1347,10 +1347,10 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>2259</v>
+        <v>2259.4</v>
       </c>
       <c r="D32" t="n">
-        <v>63754.54</v>
+        <v>63765.83</v>
       </c>
       <c r="E32" t="n">
         <v>39.77</v>
@@ -1376,16 +1376,16 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>950.4</v>
+        <v>949.95</v>
       </c>
       <c r="D33" t="n">
-        <v>60829.69</v>
+        <v>60800.89</v>
       </c>
       <c r="E33" t="n">
         <v>43.8</v>
       </c>
       <c r="F33" t="n">
-        <v>36.2</v>
+        <v>36.19</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1405,16 +1405,16 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1622.35</v>
+        <v>1619.15</v>
       </c>
       <c r="D34" t="n">
-        <v>58989.02</v>
+        <v>58872.67</v>
       </c>
       <c r="E34" t="n">
         <v>17.28</v>
       </c>
       <c r="F34" t="n">
-        <v>22.33</v>
+        <v>22.29</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1434,16 +1434,16 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>4347.65</v>
+        <v>4346.45</v>
       </c>
       <c r="D35" t="n">
-        <v>58253.63</v>
+        <v>58237.55</v>
       </c>
       <c r="E35" t="n">
         <v>24.15</v>
       </c>
       <c r="F35" t="n">
-        <v>81.94</v>
+        <v>81.92</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1463,16 +1463,16 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>3625</v>
+        <v>3608.3</v>
       </c>
       <c r="D36" t="n">
-        <v>56660.06</v>
+        <v>56399.03</v>
       </c>
       <c r="E36" t="n">
         <v>27.9</v>
       </c>
       <c r="F36" t="n">
-        <v>43.86</v>
+        <v>43.66</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1492,16 +1492,16 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1098.6</v>
+        <v>1093.65</v>
       </c>
       <c r="D37" t="n">
-        <v>54323.7</v>
+        <v>54078.93</v>
       </c>
       <c r="E37" t="n">
         <v>24.98</v>
       </c>
       <c r="F37" t="n">
-        <v>84.19</v>
+        <v>83.81</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1521,16 +1521,16 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>850.1</v>
+        <v>847.05</v>
       </c>
       <c r="D38" t="n">
-        <v>53060.64</v>
+        <v>52870.27</v>
       </c>
       <c r="E38" t="n">
         <v>15.11</v>
       </c>
       <c r="F38" t="n">
-        <v>65.7</v>
+        <v>65.45999999999999</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1550,16 +1550,16 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>37.06</v>
+        <v>36.88</v>
       </c>
       <c r="D39" t="n">
-        <v>50536.33</v>
+        <v>50290.86</v>
       </c>
       <c r="E39" t="n">
         <v>34.15</v>
       </c>
       <c r="F39" t="n">
-        <v>16.14</v>
+        <v>16.08</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -1579,16 +1579,16 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>2966.9</v>
+        <v>2965.55</v>
       </c>
       <c r="D40" t="n">
-        <v>48957.07</v>
+        <v>48934.8</v>
       </c>
       <c r="E40" t="n">
         <v>15.11</v>
       </c>
       <c r="F40" t="n">
-        <v>42.65</v>
+        <v>42.64</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -1608,16 +1608,16 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>3989.25</v>
+        <v>3982.3</v>
       </c>
       <c r="D41" t="n">
-        <v>48918.92</v>
+        <v>48833.69</v>
       </c>
       <c r="E41" t="n">
         <v>28.56</v>
       </c>
       <c r="F41" t="n">
-        <v>102.53</v>
+        <v>102.35</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -1637,16 +1637,16 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>318</v>
+        <v>316.25</v>
       </c>
       <c r="D42" t="n">
-        <v>42760.13</v>
+        <v>42524.81</v>
       </c>
       <c r="E42" t="n">
         <v>33.88</v>
       </c>
       <c r="F42" t="n">
-        <v>311.2</v>
+        <v>309.49</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -1666,16 +1666,16 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>8158.65</v>
+        <v>8198.950000000001</v>
       </c>
       <c r="D43" t="n">
-        <v>41865.79</v>
+        <v>42072.59</v>
       </c>
       <c r="E43" t="n">
         <v>20.96</v>
       </c>
       <c r="F43" t="n">
-        <v>52.71</v>
+        <v>52.97</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -1695,16 +1695,16 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>3339</v>
+        <v>3339.5</v>
       </c>
       <c r="D44" t="n">
-        <v>41723.77</v>
+        <v>41730.03</v>
       </c>
       <c r="E44" t="n">
         <v>34.51</v>
       </c>
       <c r="F44" t="n">
-        <v>36.73</v>
+        <v>36.74</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -1724,16 +1724,16 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>88.09999999999999</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="D45" t="n">
-        <v>41273.17</v>
+        <v>41179.48</v>
       </c>
       <c r="E45" t="n">
         <v>15.18</v>
       </c>
       <c r="F45" t="n">
-        <v>45.98</v>
+        <v>45.87</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -1753,16 +1753,16 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>3224.65</v>
+        <v>3222.9</v>
       </c>
       <c r="D46" t="n">
-        <v>40961.74</v>
+        <v>40939.51</v>
       </c>
       <c r="E46" t="n">
         <v>20.73</v>
       </c>
       <c r="F46" t="n">
-        <v>36.22</v>
+        <v>36.2</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -1782,16 +1782,16 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>408.5</v>
+        <v>409</v>
       </c>
       <c r="D47" t="n">
-        <v>39502.93</v>
+        <v>39551.27</v>
       </c>
       <c r="E47" t="n">
         <v>42.38</v>
       </c>
       <c r="F47" t="n">
-        <v>32.66</v>
+        <v>32.7</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -1811,16 +1811,16 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>832.1</v>
+        <v>830.85</v>
       </c>
       <c r="D48" t="n">
-        <v>37773.31</v>
+        <v>37716.57</v>
       </c>
       <c r="E48" t="n">
         <v>32.71</v>
       </c>
       <c r="F48" t="n">
-        <v>22.7</v>
+        <v>22.67</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -1840,16 +1840,16 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>2247.05</v>
+        <v>2245.4</v>
       </c>
       <c r="D49" t="n">
-        <v>37310.34</v>
+        <v>37282.94</v>
       </c>
       <c r="E49" t="n">
         <v>57.47</v>
       </c>
       <c r="F49" t="n">
-        <v>82.29000000000001</v>
+        <v>82.22</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -1869,16 +1869,16 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>1357.7</v>
+        <v>1358</v>
       </c>
       <c r="D50" t="n">
-        <v>36474.58</v>
+        <v>36482.64</v>
       </c>
       <c r="E50" t="n">
         <v>19.22</v>
       </c>
       <c r="F50" t="n">
-        <v>61.6</v>
+        <v>61.62</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -1898,16 +1898,16 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1872.7</v>
+        <v>1867.7</v>
       </c>
       <c r="D51" t="n">
-        <v>35527.12</v>
+        <v>35432.26</v>
       </c>
       <c r="E51" t="n">
         <v>24.02</v>
       </c>
       <c r="F51" t="n">
-        <v>34.47</v>
+        <v>34.38</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -1927,16 +1927,16 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>4778.5</v>
+        <v>4771.5</v>
       </c>
       <c r="D52" t="n">
-        <v>34945.2</v>
+        <v>34894.01</v>
       </c>
       <c r="E52" t="n">
         <v>32.55</v>
       </c>
       <c r="F52" t="n">
-        <v>39.02</v>
+        <v>38.96</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -1956,16 +1956,16 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>2278.4</v>
+        <v>2276.05</v>
       </c>
       <c r="D53" t="n">
-        <v>32048.67</v>
+        <v>32015.6</v>
       </c>
       <c r="E53" t="n">
         <v>17.8</v>
       </c>
       <c r="F53" t="n">
-        <v>32.53</v>
+        <v>32.5</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -1985,16 +1985,16 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1487.2</v>
+        <v>1483.65</v>
       </c>
       <c r="D54" t="n">
-        <v>31598.96</v>
+        <v>31523.54</v>
       </c>
       <c r="E54" t="n">
         <v>19.65</v>
       </c>
       <c r="F54" t="n">
-        <v>85.94</v>
+        <v>85.73999999999999</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -2014,16 +2014,16 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>3821.35</v>
+        <v>3803.2</v>
       </c>
       <c r="D55" t="n">
-        <v>31285.85</v>
+        <v>31137.25</v>
       </c>
       <c r="E55" t="n">
         <v>31.56</v>
       </c>
       <c r="F55" t="n">
-        <v>81.08</v>
+        <v>80.69</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -2046,7 +2046,7 @@
         <v>1460</v>
       </c>
       <c r="D56" t="n">
-        <v>29864.01</v>
+        <v>29864.02</v>
       </c>
       <c r="E56" t="n">
         <v>24.36</v>
@@ -2072,16 +2072,16 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1696.85</v>
+        <v>1693.9</v>
       </c>
       <c r="D57" t="n">
-        <v>29128.68</v>
+        <v>29078.04</v>
       </c>
       <c r="E57" t="n">
         <v>31.51</v>
       </c>
       <c r="F57" t="n">
-        <v>38.18</v>
+        <v>38.11</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -2101,16 +2101,16 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>539</v>
+        <v>536.5</v>
       </c>
       <c r="D58" t="n">
-        <v>27196.54</v>
+        <v>27070.4</v>
       </c>
       <c r="E58" t="n">
         <v>22.12</v>
       </c>
       <c r="F58" t="n">
-        <v>31.83</v>
+        <v>31.69</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -2130,16 +2130,16 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>4415.65</v>
+        <v>4398</v>
       </c>
       <c r="D59" t="n">
-        <v>26249.95</v>
+        <v>26145.03</v>
       </c>
       <c r="E59" t="n">
         <v>37.48</v>
       </c>
       <c r="F59" t="n">
-        <v>71.63</v>
+        <v>71.34999999999999</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -2159,10 +2159,10 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>1517.2</v>
+        <v>1517.15</v>
       </c>
       <c r="D60" t="n">
-        <v>25114.49</v>
+        <v>25113.67</v>
       </c>
       <c r="E60" t="n">
         <v>28.35</v>
@@ -2188,10 +2188,10 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>19300.45</v>
+        <v>19300</v>
       </c>
       <c r="D61" t="n">
-        <v>24762.28</v>
+        <v>24761.7</v>
       </c>
       <c r="E61" t="n">
         <v>26.47</v>
@@ -2208,25 +2208,25 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Pattern</t>
+          <t>TVS Holdings</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>DATAPATTNS</t>
+          <t>TVSHLTD</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>4066.15</v>
+        <v>11283.65</v>
       </c>
       <c r="D62" t="n">
-        <v>22763.96</v>
+        <v>22829.17</v>
       </c>
       <c r="E62" t="n">
-        <v>21.92</v>
+        <v>16.95</v>
       </c>
       <c r="F62" t="n">
-        <v>84.2</v>
+        <v>11.48</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -2246,16 +2246,16 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>831.85</v>
+        <v>830</v>
       </c>
       <c r="D63" t="n">
-        <v>22691.22</v>
+        <v>22640.75</v>
       </c>
       <c r="E63" t="n">
         <v>15.51</v>
       </c>
       <c r="F63" t="n">
-        <v>34.87</v>
+        <v>34.78</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -2266,25 +2266,25 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>TVS Holdings</t>
+          <t>Data Pattern</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>TVSHLTD</t>
+          <t>DATAPATTNS</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>11215</v>
+        <v>4015.5</v>
       </c>
       <c r="D64" t="n">
-        <v>22690.28</v>
+        <v>22480.42</v>
       </c>
       <c r="E64" t="n">
-        <v>16.95</v>
+        <v>21.92</v>
       </c>
       <c r="F64" t="n">
-        <v>11.41</v>
+        <v>83.17</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -2304,16 +2304,16 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>702.15</v>
+        <v>694.2</v>
       </c>
       <c r="D65" t="n">
-        <v>22570.56</v>
+        <v>22315.01</v>
       </c>
       <c r="E65" t="n">
         <v>34.02</v>
       </c>
       <c r="F65" t="n">
-        <v>82.02</v>
+        <v>81.09</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -2324,25 +2324,25 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>GE Shipping Co</t>
+          <t>Metro Brands</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>GESHIP</t>
+          <t>METROBRAND</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>1546.3</v>
+        <v>809.85</v>
       </c>
       <c r="D66" t="n">
-        <v>22076.08</v>
+        <v>22077.46</v>
       </c>
       <c r="E66" t="n">
-        <v>15.79</v>
+        <v>20.12</v>
       </c>
       <c r="F66" t="n">
-        <v>5.87</v>
+        <v>53.28</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -2353,25 +2353,25 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Metro Brands</t>
+          <t>GE Shipping Co</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>METROBRAND</t>
+          <t>GESHIP</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>807.5</v>
+        <v>1545.9</v>
       </c>
       <c r="D67" t="n">
-        <v>22013.4</v>
+        <v>22070.36</v>
       </c>
       <c r="E67" t="n">
-        <v>20.12</v>
+        <v>15.79</v>
       </c>
       <c r="F67" t="n">
-        <v>53.13</v>
+        <v>5.88</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -2391,16 +2391,16 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>784.2</v>
+        <v>782.15</v>
       </c>
       <c r="D68" t="n">
-        <v>21737.59</v>
+        <v>21680.75</v>
       </c>
       <c r="E68" t="n">
         <v>59.3</v>
       </c>
       <c r="F68" t="n">
-        <v>27.18</v>
+        <v>27.11</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -2420,16 +2420,16 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>6835</v>
+        <v>6795</v>
       </c>
       <c r="D69" t="n">
-        <v>21024.18</v>
+        <v>20901.14</v>
       </c>
       <c r="E69" t="n">
         <v>15.15</v>
       </c>
       <c r="F69" t="n">
-        <v>153.14</v>
+        <v>152.24</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -2449,16 +2449,16 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>292</v>
+        <v>290.95</v>
       </c>
       <c r="D70" t="n">
-        <v>20645.19</v>
+        <v>20570.94</v>
       </c>
       <c r="E70" t="n">
         <v>16.8</v>
       </c>
       <c r="F70" t="n">
-        <v>25.9</v>
+        <v>25.81</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -2478,16 +2478,16 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>1357.4</v>
+        <v>1356</v>
       </c>
       <c r="D71" t="n">
-        <v>19532.39</v>
+        <v>19512.24</v>
       </c>
       <c r="E71" t="n">
         <v>16.84</v>
       </c>
       <c r="F71" t="n">
-        <v>40.89</v>
+        <v>40.84</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -2507,16 +2507,16 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>2345.1</v>
+        <v>2345.65</v>
       </c>
       <c r="D72" t="n">
-        <v>17825.48</v>
+        <v>17829.66</v>
       </c>
       <c r="E72" t="n">
         <v>24.24</v>
       </c>
       <c r="F72" t="n">
-        <v>26.83</v>
+        <v>26.84</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -2536,16 +2536,16 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>1887.05</v>
+        <v>1885.5</v>
       </c>
       <c r="D73" t="n">
-        <v>17747.88</v>
+        <v>17733.3</v>
       </c>
       <c r="E73" t="n">
         <v>34.42</v>
       </c>
       <c r="F73" t="n">
-        <v>24.37</v>
+        <v>24.36</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -2565,16 +2565,16 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>394.6</v>
+        <v>394.5</v>
       </c>
       <c r="D74" t="n">
-        <v>17052.95</v>
+        <v>17048.62</v>
       </c>
       <c r="E74" t="n">
         <v>69.25</v>
       </c>
       <c r="F74" t="n">
-        <v>25.58</v>
+        <v>25.59</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -2594,16 +2594,16 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>1796.35</v>
+        <v>1794.35</v>
       </c>
       <c r="D75" t="n">
-        <v>16957.77</v>
+        <v>16938.89</v>
       </c>
       <c r="E75" t="n">
         <v>18.03</v>
       </c>
       <c r="F75" t="n">
-        <v>51.78</v>
+        <v>51.72</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -2623,16 +2623,16 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>242</v>
+        <v>240.65</v>
       </c>
       <c r="D76" t="n">
-        <v>16754.71</v>
+        <v>16661.25</v>
       </c>
       <c r="E76" t="n">
         <v>44.62</v>
       </c>
       <c r="F76" t="n">
-        <v>11.74</v>
+        <v>11.69</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -2652,16 +2652,16 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>1540</v>
+        <v>1534.3</v>
       </c>
       <c r="D77" t="n">
-        <v>16722.49</v>
+        <v>16660.6</v>
       </c>
       <c r="E77" t="n">
         <v>18.33</v>
       </c>
       <c r="F77" t="n">
-        <v>62.15</v>
+        <v>61.92</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -2681,16 +2681,16 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>520.7</v>
+        <v>518.8</v>
       </c>
       <c r="D78" t="n">
-        <v>16501.46</v>
+        <v>16441.23</v>
       </c>
       <c r="E78" t="n">
         <v>22.07</v>
       </c>
       <c r="F78" t="n">
-        <v>35.57</v>
+        <v>35.44</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -2710,16 +2710,16 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>712.1</v>
+        <v>708.4</v>
       </c>
       <c r="D79" t="n">
-        <v>15863.94</v>
+        <v>15781.52</v>
       </c>
       <c r="E79" t="n">
         <v>17.94</v>
       </c>
       <c r="F79" t="n">
-        <v>69.62</v>
+        <v>69.26000000000001</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
@@ -2739,16 +2739,16 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>1309</v>
+        <v>1291.8</v>
       </c>
       <c r="D80" t="n">
-        <v>15342.97</v>
+        <v>15141.36</v>
       </c>
       <c r="E80" t="n">
         <v>30.19</v>
       </c>
       <c r="F80" t="n">
-        <v>124.37</v>
+        <v>122.75</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -2768,16 +2768,16 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>1434.3</v>
+        <v>1442.55</v>
       </c>
       <c r="D81" t="n">
-        <v>14773.02</v>
+        <v>14858</v>
       </c>
       <c r="E81" t="n">
         <v>20.53</v>
       </c>
       <c r="F81" t="n">
-        <v>78.77</v>
+        <v>79.22</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -2797,16 +2797,16 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>3103.15</v>
+        <v>3093</v>
       </c>
       <c r="D82" t="n">
-        <v>14273.05</v>
+        <v>14226.37</v>
       </c>
       <c r="E82" t="n">
         <v>30.29</v>
       </c>
       <c r="F82" t="n">
-        <v>80.26000000000001</v>
+        <v>80</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -2826,16 +2826,16 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>251.4</v>
+        <v>249.55</v>
       </c>
       <c r="D83" t="n">
-        <v>14129.77</v>
+        <v>14025.8</v>
       </c>
       <c r="E83" t="n">
         <v>30.4</v>
       </c>
       <c r="F83" t="n">
-        <v>18.04</v>
+        <v>17.91</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -2855,16 +2855,16 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>3559.6</v>
+        <v>3543</v>
       </c>
       <c r="D84" t="n">
-        <v>13904.73</v>
+        <v>13839.88</v>
       </c>
       <c r="E84" t="n">
         <v>22.3</v>
       </c>
       <c r="F84" t="n">
-        <v>39.73</v>
+        <v>39.54</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -2884,16 +2884,16 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>3110.6</v>
+        <v>3105</v>
       </c>
       <c r="D85" t="n">
-        <v>13739.7</v>
+        <v>13714.97</v>
       </c>
       <c r="E85" t="n">
         <v>35.31</v>
       </c>
       <c r="F85" t="n">
-        <v>116.85</v>
+        <v>116.65</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
@@ -2913,16 +2913,16 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>301</v>
+        <v>300.15</v>
       </c>
       <c r="D86" t="n">
-        <v>13640.24</v>
+        <v>13601.73</v>
       </c>
       <c r="E86" t="n">
         <v>18.8</v>
       </c>
       <c r="F86" t="n">
-        <v>26.41</v>
+        <v>26.33</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
@@ -2942,16 +2942,16 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>817.55</v>
+        <v>818.15</v>
       </c>
       <c r="D87" t="n">
-        <v>13319.4</v>
+        <v>13329.18</v>
       </c>
       <c r="E87" t="n">
         <v>27.87</v>
       </c>
       <c r="F87" t="n">
-        <v>83.36</v>
+        <v>83.42</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
@@ -2971,16 +2971,16 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>707.95</v>
+        <v>707.75</v>
       </c>
       <c r="D88" t="n">
-        <v>13312.42</v>
+        <v>13308.65</v>
       </c>
       <c r="E88" t="n">
         <v>18.79</v>
       </c>
       <c r="F88" t="n">
-        <v>24.79</v>
+        <v>24.77</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
@@ -3000,16 +3000,16 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>2150.35</v>
+        <v>2142.05</v>
       </c>
       <c r="D89" t="n">
-        <v>13151.62</v>
+        <v>13100.86</v>
       </c>
       <c r="E89" t="n">
         <v>33.29</v>
       </c>
       <c r="F89" t="n">
-        <v>62.13</v>
+        <v>61.89</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
@@ -3029,16 +3029,16 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>84.34</v>
+        <v>83.84999999999999</v>
       </c>
       <c r="D90" t="n">
-        <v>13081.43</v>
+        <v>13005.43</v>
       </c>
       <c r="E90" t="n">
         <v>16.1</v>
       </c>
       <c r="F90" t="n">
-        <v>58.47</v>
+        <v>58.13</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
@@ -3058,16 +3058,16 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>1903.4</v>
+        <v>1900.6</v>
       </c>
       <c r="D91" t="n">
-        <v>12973.14</v>
+        <v>12954.06</v>
       </c>
       <c r="E91" t="n">
         <v>21.19</v>
       </c>
       <c r="F91" t="n">
-        <v>35.02</v>
+        <v>34.98</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
@@ -3087,16 +3087,16 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>1649.9</v>
+        <v>1641.05</v>
       </c>
       <c r="D92" t="n">
-        <v>12687.18</v>
+        <v>12619.12</v>
       </c>
       <c r="E92" t="n">
         <v>45.28</v>
       </c>
       <c r="F92" t="n">
-        <v>58.15</v>
+        <v>57.84</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
@@ -3116,16 +3116,16 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>897.85</v>
+        <v>899.15</v>
       </c>
       <c r="D93" t="n">
-        <v>11988.82</v>
+        <v>12006.18</v>
       </c>
       <c r="E93" t="n">
         <v>15.85</v>
       </c>
       <c r="F93" t="n">
-        <v>25.93</v>
+        <v>25.97</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
@@ -3145,16 +3145,16 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>2878.1</v>
+        <v>2876.3</v>
       </c>
       <c r="D94" t="n">
-        <v>11917.27</v>
+        <v>11909.81</v>
       </c>
       <c r="E94" t="n">
         <v>37.48</v>
       </c>
       <c r="F94" t="n">
-        <v>48.68</v>
+        <v>48.65</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
@@ -3194,25 +3194,25 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Fujiyama Power</t>
+          <t>Sudeep Pharma</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>UTLSOLAR</t>
+          <t>SUDEEPPHRM</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>378.1</v>
+        <v>1015</v>
       </c>
       <c r="D96" t="n">
-        <v>11619.51</v>
+        <v>11464.31</v>
       </c>
       <c r="E96" t="n">
-        <v>35.14</v>
+        <v>28.18</v>
       </c>
       <c r="F96" t="n">
-        <v>27.78</v>
+        <v>62.77</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
@@ -3223,25 +3223,25 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Sudeep Pharma</t>
+          <t>Fujiyama Power</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>SUDEEPPHRM</t>
+          <t>UTLSOLAR</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>1013</v>
+        <v>371.7</v>
       </c>
       <c r="D97" t="n">
-        <v>11441.72</v>
+        <v>11422.83</v>
       </c>
       <c r="E97" t="n">
-        <v>28.18</v>
+        <v>35.14</v>
       </c>
       <c r="F97" t="n">
-        <v>62.64</v>
+        <v>27.32</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
@@ -3261,16 +3261,16 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>1809.7</v>
+        <v>1807.05</v>
       </c>
       <c r="D98" t="n">
-        <v>11423.28</v>
+        <v>11406.55</v>
       </c>
       <c r="E98" t="n">
         <v>35.41</v>
       </c>
       <c r="F98" t="n">
-        <v>43.19</v>
+        <v>43.13</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
@@ -3281,25 +3281,25 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>ASK Automotive</t>
+          <t>Metropolis Healt</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>ASKAUTOLTD</t>
+          <t>METROPOLIS</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>573.65</v>
+        <v>545.45</v>
       </c>
       <c r="D99" t="n">
-        <v>11309.04</v>
+        <v>11316.11</v>
       </c>
       <c r="E99" t="n">
-        <v>25.42</v>
+        <v>17.81</v>
       </c>
       <c r="F99" t="n">
-        <v>35.74</v>
+        <v>54.36</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
@@ -3310,25 +3310,25 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Metropolis Healt</t>
+          <t>ASK Automotive</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>METROPOLIS</t>
+          <t>ASKAUTOLTD</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>545.1</v>
+        <v>573.65</v>
       </c>
       <c r="D100" t="n">
-        <v>11308.85</v>
+        <v>11309.04</v>
       </c>
       <c r="E100" t="n">
-        <v>17.81</v>
+        <v>25.42</v>
       </c>
       <c r="F100" t="n">
-        <v>54.33</v>
+        <v>35.74</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
@@ -3348,16 +3348,16 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>1363</v>
+        <v>1347.2</v>
       </c>
       <c r="D101" t="n">
-        <v>10555.61</v>
+        <v>10433.25</v>
       </c>
       <c r="E101" t="n">
         <v>31.73</v>
       </c>
       <c r="F101" t="n">
-        <v>79.20999999999999</v>
+        <v>78.29000000000001</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
@@ -3377,16 +3377,16 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>1295</v>
+        <v>1289</v>
       </c>
       <c r="D102" t="n">
-        <v>10436.09</v>
+        <v>10387.74</v>
       </c>
       <c r="E102" t="n">
         <v>17.19</v>
       </c>
       <c r="F102" t="n">
-        <v>112.83</v>
+        <v>112.32</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
@@ -3406,16 +3406,16 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>12703.3</v>
+        <v>12736.35</v>
       </c>
       <c r="D103" t="n">
-        <v>10070.78</v>
+        <v>10096.98</v>
       </c>
       <c r="E103" t="n">
         <v>21.21</v>
       </c>
       <c r="F103" t="n">
-        <v>56.71</v>
+        <v>56.86</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
@@ -3435,16 +3435,16 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>198.75</v>
+        <v>199</v>
       </c>
       <c r="D104" t="n">
-        <v>9954.030000000001</v>
+        <v>9966.540000000001</v>
       </c>
       <c r="E104" t="n">
         <v>15.41</v>
       </c>
       <c r="F104" t="n">
-        <v>10.13</v>
+        <v>10.14</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
@@ -3464,16 +3464,16 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>229.9</v>
+        <v>229.45</v>
       </c>
       <c r="D105" t="n">
-        <v>9930.07</v>
+        <v>9910.629999999999</v>
       </c>
       <c r="E105" t="n">
         <v>19.46</v>
       </c>
       <c r="F105" t="n">
-        <v>35.73</v>
+        <v>35.66</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
@@ -3493,16 +3493,16 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="D106" t="n">
-        <v>9617.99</v>
+        <v>9629.620000000001</v>
       </c>
       <c r="E106" t="n">
         <v>15.16</v>
       </c>
       <c r="F106" t="n">
-        <v>18.65</v>
+        <v>18.66</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
@@ -3522,16 +3522,16 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>314.05</v>
+        <v>313.1</v>
       </c>
       <c r="D107" t="n">
-        <v>9426.73</v>
+        <v>9398.219999999999</v>
       </c>
       <c r="E107" t="n">
         <v>23.31</v>
       </c>
       <c r="F107" t="n">
-        <v>30.93</v>
+        <v>30.83</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
@@ -3560,7 +3560,7 @@
         <v>118.47</v>
       </c>
       <c r="F108" t="n">
-        <v>41.11</v>
+        <v>41.1</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
@@ -3580,16 +3580,16 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>6389.9</v>
+        <v>6389</v>
       </c>
       <c r="D109" t="n">
-        <v>9320.74</v>
+        <v>9319.42</v>
       </c>
       <c r="E109" t="n">
         <v>26.95</v>
       </c>
       <c r="F109" t="n">
-        <v>127.58</v>
+        <v>127.56</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
@@ -3638,16 +3638,16 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>50.62</v>
+        <v>50.32</v>
       </c>
       <c r="D111" t="n">
-        <v>8910.309999999999</v>
+        <v>8857.51</v>
       </c>
       <c r="E111" t="n">
         <v>18.27</v>
       </c>
       <c r="F111" t="n">
-        <v>22.69</v>
+        <v>22.54</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
@@ -3667,16 +3667,16 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>91.66</v>
+        <v>90.84</v>
       </c>
       <c r="D112" t="n">
-        <v>8900.16</v>
+        <v>8820.540000000001</v>
       </c>
       <c r="E112" t="n">
         <v>20.69</v>
       </c>
       <c r="F112" t="n">
-        <v>12.75</v>
+        <v>12.64</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
@@ -3696,16 +3696,16 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>213.65</v>
+        <v>212.75</v>
       </c>
       <c r="D113" t="n">
-        <v>8796.84</v>
+        <v>8759.790000000001</v>
       </c>
       <c r="E113" t="n">
         <v>29.79</v>
       </c>
       <c r="F113" t="n">
-        <v>12.51</v>
+        <v>12.47</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
@@ -3716,25 +3716,25 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Omnitech Engg.</t>
+          <t>Kennametal India</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>OMNI</t>
+          <t>KENNAMET</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>681.55</v>
+        <v>3838</v>
       </c>
       <c r="D114" t="n">
-        <v>8428.530000000001</v>
+        <v>8435.219999999999</v>
       </c>
       <c r="E114" t="n">
-        <v>17.55</v>
+        <v>33.21</v>
       </c>
       <c r="F114" t="n">
-        <v>81.09999999999999</v>
+        <v>43.08</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
@@ -3745,25 +3745,25 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Kennametal India</t>
+          <t>Omnitech Engg.</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>KENNAMET</t>
+          <t>OMNI</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>3827.9</v>
+        <v>682</v>
       </c>
       <c r="D115" t="n">
-        <v>8413.02</v>
+        <v>8434.09</v>
       </c>
       <c r="E115" t="n">
-        <v>33.21</v>
+        <v>17.55</v>
       </c>
       <c r="F115" t="n">
-        <v>42.97</v>
+        <v>81.15000000000001</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
@@ -3783,16 +3783,16 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>3268.95</v>
+        <v>3225.65</v>
       </c>
       <c r="D116" t="n">
-        <v>8291.459999999999</v>
+        <v>8181.64</v>
       </c>
       <c r="E116" t="n">
         <v>16.32</v>
       </c>
       <c r="F116" t="n">
-        <v>64.04000000000001</v>
+        <v>63.19</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
@@ -3812,16 +3812,16 @@
         </is>
       </c>
       <c r="C117" t="n">
-        <v>268.45</v>
+        <v>268.7</v>
       </c>
       <c r="D117" t="n">
-        <v>8167.36</v>
+        <v>8174.98</v>
       </c>
       <c r="E117" t="n">
         <v>25.27</v>
       </c>
       <c r="F117" t="n">
-        <v>12.56</v>
+        <v>12.57</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
@@ -3841,16 +3841,16 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>979</v>
+        <v>977</v>
       </c>
       <c r="D118" t="n">
-        <v>8035.69</v>
+        <v>8019.28</v>
       </c>
       <c r="E118" t="n">
         <v>21.05</v>
       </c>
       <c r="F118" t="n">
-        <v>45.35</v>
+        <v>45.25</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
@@ -3870,16 +3870,16 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>162.3</v>
+        <v>161.7</v>
       </c>
       <c r="D119" t="n">
-        <v>8011.68</v>
+        <v>7982.06</v>
       </c>
       <c r="E119" t="n">
         <v>16.52</v>
       </c>
       <c r="F119" t="n">
-        <v>16.4</v>
+        <v>16.34</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
@@ -3899,16 +3899,16 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>162</v>
+        <v>162.15</v>
       </c>
       <c r="D120" t="n">
-        <v>7874.89</v>
+        <v>7882.18</v>
       </c>
       <c r="E120" t="n">
         <v>24.23</v>
       </c>
       <c r="F120" t="n">
-        <v>10.63</v>
+        <v>10.64</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
@@ -3919,25 +3919,25 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Guj Pipavav Port</t>
+          <t>Raghav Product.</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>GPPL</t>
+          <t>RPEL</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>160.95</v>
+        <v>1690</v>
       </c>
       <c r="D121" t="n">
-        <v>7780.94</v>
+        <v>7760.81</v>
       </c>
       <c r="E121" t="n">
-        <v>28.06</v>
+        <v>30.3</v>
       </c>
       <c r="F121" t="n">
-        <v>14.31</v>
+        <v>110.11</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
@@ -3948,25 +3948,25 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Raghav Product.</t>
+          <t>Guj Pipavav Port</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>RPEL</t>
+          <t>GPPL</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>1690</v>
+        <v>160.5</v>
       </c>
       <c r="D122" t="n">
-        <v>7760.81</v>
+        <v>7759.19</v>
       </c>
       <c r="E122" t="n">
-        <v>30.3</v>
+        <v>28.06</v>
       </c>
       <c r="F122" t="n">
-        <v>110.11</v>
+        <v>14.26</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
@@ -3977,25 +3977,25 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Sanofi Consumer</t>
+          <t>Thyrocare Tech.</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>SANOFICONR</t>
+          <t>THYROCARE</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>3356.65</v>
+        <v>485.15</v>
       </c>
       <c r="D123" t="n">
-        <v>7730.58</v>
+        <v>7722.01</v>
       </c>
       <c r="E123" t="n">
-        <v>89.93000000000001</v>
+        <v>35.38</v>
       </c>
       <c r="F123" t="n">
-        <v>29.08</v>
+        <v>42.74</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
@@ -4006,25 +4006,25 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Thyrocare Tech.</t>
+          <t>Sanofi Consumer</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>THYROCARE</t>
+          <t>SANOFICONR</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>484.7</v>
+        <v>3350.9</v>
       </c>
       <c r="D124" t="n">
-        <v>7714.84</v>
+        <v>7717.34</v>
       </c>
       <c r="E124" t="n">
-        <v>35.38</v>
+        <v>89.93000000000001</v>
       </c>
       <c r="F124" t="n">
-        <v>42.71</v>
+        <v>29.03</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
@@ -4044,16 +4044,16 @@
         </is>
       </c>
       <c r="C125" t="n">
-        <v>167.13</v>
+        <v>167.44</v>
       </c>
       <c r="D125" t="n">
-        <v>7668.89</v>
+        <v>7683.11</v>
       </c>
       <c r="E125" t="n">
         <v>19.34</v>
       </c>
       <c r="F125" t="n">
-        <v>49.47</v>
+        <v>49.56</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
@@ -4073,16 +4073,16 @@
         </is>
       </c>
       <c r="C126" t="n">
-        <v>943.2</v>
+        <v>938.2</v>
       </c>
       <c r="D126" t="n">
-        <v>7468.86</v>
+        <v>7429.26</v>
       </c>
       <c r="E126" t="n">
         <v>54.32</v>
       </c>
       <c r="F126" t="n">
-        <v>51.17</v>
+        <v>50.9</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
@@ -4131,10 +4131,10 @@
         </is>
       </c>
       <c r="C128" t="n">
-        <v>673.1</v>
+        <v>672.35</v>
       </c>
       <c r="D128" t="n">
-        <v>7025.7</v>
+        <v>7017.87</v>
       </c>
       <c r="E128" t="n">
         <v>83.20999999999999</v>
@@ -4160,16 +4160,16 @@
         </is>
       </c>
       <c r="C129" t="n">
-        <v>627.7</v>
+        <v>632</v>
       </c>
       <c r="D129" t="n">
-        <v>6677.71</v>
+        <v>6723.46</v>
       </c>
       <c r="E129" t="n">
         <v>16.93</v>
       </c>
       <c r="F129" t="n">
-        <v>48.53</v>
+        <v>48.86</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
@@ -4189,16 +4189,16 @@
         </is>
       </c>
       <c r="C130" t="n">
-        <v>377.75</v>
+        <v>377.5</v>
       </c>
       <c r="D130" t="n">
-        <v>6580.6</v>
+        <v>6576.24</v>
       </c>
       <c r="E130" t="n">
         <v>16.95</v>
       </c>
       <c r="F130" t="n">
-        <v>20.49</v>
+        <v>20.48</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
@@ -4238,25 +4238,25 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Timex Group</t>
+          <t>Krishana Phosch.</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>TIMEX</t>
+          <t>KRISHANA</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>641.55</v>
+        <v>210.27</v>
       </c>
       <c r="D132" t="n">
-        <v>6476.49</v>
+        <v>6500.23</v>
       </c>
       <c r="E132" t="n">
-        <v>82.84999999999999</v>
+        <v>27.24</v>
       </c>
       <c r="F132" t="n">
-        <v>72.54000000000001</v>
+        <v>33.06</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
@@ -4267,25 +4267,25 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Krishana Phosch.</t>
+          <t>Timex Group</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>KRISHANA</t>
+          <t>TIMEX</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>209.06</v>
+        <v>640.1</v>
       </c>
       <c r="D133" t="n">
-        <v>6462.82</v>
+        <v>6461.86</v>
       </c>
       <c r="E133" t="n">
-        <v>27.24</v>
+        <v>82.84999999999999</v>
       </c>
       <c r="F133" t="n">
-        <v>32.87</v>
+        <v>72.38</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
@@ -4305,16 +4305,16 @@
         </is>
       </c>
       <c r="C134" t="n">
-        <v>1988.8</v>
+        <v>1989.3</v>
       </c>
       <c r="D134" t="n">
-        <v>6413.79</v>
+        <v>6415.4</v>
       </c>
       <c r="E134" t="n">
         <v>28.58</v>
       </c>
       <c r="F134" t="n">
-        <v>33.68</v>
+        <v>33.69</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
@@ -4334,16 +4334,16 @@
         </is>
       </c>
       <c r="C135" t="n">
-        <v>481.65</v>
+        <v>477.55</v>
       </c>
       <c r="D135" t="n">
-        <v>6373.61</v>
+        <v>6319.35</v>
       </c>
       <c r="E135" t="n">
         <v>18.92</v>
       </c>
       <c r="F135" t="n">
-        <v>94.93000000000001</v>
+        <v>94.12</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
@@ -4363,16 +4363,16 @@
         </is>
       </c>
       <c r="C136" t="n">
-        <v>307.25</v>
+        <v>306.6</v>
       </c>
       <c r="D136" t="n">
-        <v>6286.61</v>
+        <v>6273.31</v>
       </c>
       <c r="E136" t="n">
         <v>22.66</v>
       </c>
       <c r="F136" t="n">
-        <v>19.89</v>
+        <v>19.85</v>
       </c>
       <c r="G136" t="inlineStr">
         <is>
@@ -4392,16 +4392,16 @@
         </is>
       </c>
       <c r="C137" t="n">
-        <v>1291.05</v>
+        <v>1290.6</v>
       </c>
       <c r="D137" t="n">
-        <v>5945.74</v>
+        <v>5943.66</v>
       </c>
       <c r="E137" t="n">
         <v>15.13</v>
       </c>
       <c r="F137" t="n">
-        <v>47.03</v>
+        <v>47.01</v>
       </c>
       <c r="G137" t="inlineStr">
         <is>
@@ -4421,16 +4421,16 @@
         </is>
       </c>
       <c r="C138" t="n">
-        <v>1093.55</v>
+        <v>1096</v>
       </c>
       <c r="D138" t="n">
-        <v>5900.13</v>
+        <v>5913.35</v>
       </c>
       <c r="E138" t="n">
         <v>18.37</v>
       </c>
       <c r="F138" t="n">
-        <v>11.29</v>
+        <v>11.31</v>
       </c>
       <c r="G138" t="inlineStr">
         <is>
@@ -4441,25 +4441,25 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Borosil Renew.</t>
+          <t>Shivalik Bimetal</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>BORORENEW</t>
+          <t>SBCL</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>394</v>
+        <v>1005.45</v>
       </c>
       <c r="D139" t="n">
-        <v>5799.08</v>
+        <v>5791.79</v>
       </c>
       <c r="E139" t="n">
-        <v>26.62</v>
+        <v>26.57</v>
       </c>
       <c r="F139" t="n">
-        <v>14.41</v>
+        <v>54.33</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
@@ -4470,25 +4470,25 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>V2 Retail</t>
+          <t>Borosil Renew.</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>V2RETAIL</t>
+          <t>BORORENEW</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>158.85</v>
+        <v>393.45</v>
       </c>
       <c r="D140" t="n">
-        <v>5792.22</v>
+        <v>5790.98</v>
       </c>
       <c r="E140" t="n">
-        <v>19.53</v>
+        <v>26.62</v>
       </c>
       <c r="F140" t="n">
-        <v>35.34</v>
+        <v>14.39</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
@@ -4499,25 +4499,25 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Shivalik Bimetal</t>
+          <t>Sharda Cropchem</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>SBCL</t>
+          <t>SHARDACROP</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>1005.45</v>
+        <v>640.45</v>
       </c>
       <c r="D141" t="n">
-        <v>5791.79</v>
+        <v>5778.15</v>
       </c>
       <c r="E141" t="n">
-        <v>26.57</v>
+        <v>30.25</v>
       </c>
       <c r="F141" t="n">
-        <v>54.33</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
@@ -4528,25 +4528,25 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Lohia Corp</t>
+          <t>SPARC</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>LCL</t>
+          <t>SPARC</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>546.3</v>
+        <v>177.6</v>
       </c>
       <c r="D142" t="n">
-        <v>5771.68</v>
+        <v>5763.48</v>
       </c>
       <c r="E142" t="n">
-        <v>43.77</v>
+        <v>164.99</v>
       </c>
       <c r="F142" t="n">
-        <v>23.28</v>
+        <v>3.6</v>
       </c>
       <c r="G142" t="inlineStr">
         <is>
@@ -4557,25 +4557,25 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Rentomojo</t>
+          <t>V2 Retail</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>RENTOMOJO</t>
+          <t>V2RETAIL</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>553.9</v>
+        <v>157.95</v>
       </c>
       <c r="D143" t="n">
-        <v>5766.89</v>
+        <v>5759.4</v>
       </c>
       <c r="E143" t="n">
-        <v>21.51</v>
+        <v>19.53</v>
       </c>
       <c r="F143" t="n">
-        <v>51.34</v>
+        <v>35.14</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
@@ -4586,25 +4586,25 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Sharda Cropchem</t>
+          <t>Rentomojo</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>SHARDACROP</t>
+          <t>RENTOMOJO</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>637.95</v>
+        <v>552.7</v>
       </c>
       <c r="D144" t="n">
-        <v>5755.59</v>
+        <v>5754.4</v>
       </c>
       <c r="E144" t="n">
-        <v>30.25</v>
+        <v>21.51</v>
       </c>
       <c r="F144" t="n">
-        <v>9.18</v>
+        <v>51.22</v>
       </c>
       <c r="G144" t="inlineStr">
         <is>
@@ -4615,25 +4615,25 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>SPARC</t>
+          <t>Redtape</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>SPARC</t>
+          <t>REDTAPE</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>177.35</v>
+        <v>104</v>
       </c>
       <c r="D145" t="n">
-        <v>5755.37</v>
+        <v>5749.2</v>
       </c>
       <c r="E145" t="n">
-        <v>164.99</v>
+        <v>24.48</v>
       </c>
       <c r="F145" t="n">
-        <v>3.58</v>
+        <v>23.34</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
@@ -4644,25 +4644,25 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Redtape</t>
+          <t>Lohia Corp</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>REDTAPE</t>
+          <t>LCL</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>103.8</v>
+        <v>540.95</v>
       </c>
       <c r="D146" t="n">
-        <v>5738.14</v>
+        <v>5715.16</v>
       </c>
       <c r="E146" t="n">
-        <v>24.48</v>
+        <v>43.77</v>
       </c>
       <c r="F146" t="n">
-        <v>23.29</v>
+        <v>23.05</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
@@ -4682,16 +4682,16 @@
         </is>
       </c>
       <c r="C147" t="n">
-        <v>47.84</v>
+        <v>47.8</v>
       </c>
       <c r="D147" t="n">
-        <v>5571.04</v>
+        <v>5566.37</v>
       </c>
       <c r="E147" t="n">
         <v>18.3</v>
       </c>
       <c r="F147" t="n">
-        <v>45.57</v>
+        <v>45.53</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
@@ -4711,16 +4711,16 @@
         </is>
       </c>
       <c r="C148" t="n">
-        <v>561.55</v>
+        <v>558.6</v>
       </c>
       <c r="D148" t="n">
-        <v>5535.3</v>
+        <v>5506.22</v>
       </c>
       <c r="E148" t="n">
         <v>18.01</v>
       </c>
       <c r="F148" t="n">
-        <v>39.41</v>
+        <v>39.21</v>
       </c>
       <c r="G148" t="inlineStr">
         <is>
@@ -4740,16 +4740,16 @@
         </is>
       </c>
       <c r="C149" t="n">
-        <v>437.85</v>
+        <v>436</v>
       </c>
       <c r="D149" t="n">
-        <v>5315.1</v>
+        <v>5292.65</v>
       </c>
       <c r="E149" t="n">
         <v>22.72</v>
       </c>
       <c r="F149" t="n">
-        <v>19.91</v>
+        <v>19.83</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
@@ -4769,16 +4769,16 @@
         </is>
       </c>
       <c r="C150" t="n">
-        <v>7215</v>
+        <v>7192.05</v>
       </c>
       <c r="D150" t="n">
-        <v>5187.59</v>
+        <v>5171.09</v>
       </c>
       <c r="E150" t="n">
         <v>21.96</v>
       </c>
       <c r="F150" t="n">
-        <v>23.68</v>
+        <v>23.6</v>
       </c>
       <c r="G150" t="inlineStr">
         <is>
@@ -4798,16 +4798,16 @@
         </is>
       </c>
       <c r="C151" t="n">
-        <v>388.45</v>
+        <v>386.4</v>
       </c>
       <c r="D151" t="n">
-        <v>5073.88</v>
+        <v>5047.1</v>
       </c>
       <c r="E151" t="n">
         <v>30.05</v>
       </c>
       <c r="F151" t="n">
-        <v>20.18</v>
+        <v>20.07</v>
       </c>
       <c r="G151" t="inlineStr">
         <is>
@@ -4827,16 +4827,16 @@
         </is>
       </c>
       <c r="C152" t="n">
-        <v>126.1</v>
+        <v>125.75</v>
       </c>
       <c r="D152" t="n">
-        <v>5043.81</v>
+        <v>5029.81</v>
       </c>
       <c r="E152" t="n">
         <v>26.05</v>
       </c>
       <c r="F152" t="n">
-        <v>20.87</v>
+        <v>20.81</v>
       </c>
       <c r="G152" t="inlineStr">
         <is>
@@ -4856,10 +4856,10 @@
         </is>
       </c>
       <c r="C153" t="n">
-        <v>1608</v>
+        <v>1607.8</v>
       </c>
       <c r="D153" t="n">
-        <v>4845.33</v>
+        <v>4844.73</v>
       </c>
       <c r="E153" t="n">
         <v>26.3</v>
@@ -4914,16 +4914,16 @@
         </is>
       </c>
       <c r="C155" t="n">
-        <v>1700</v>
+        <v>1698</v>
       </c>
       <c r="D155" t="n">
-        <v>4474.35</v>
+        <v>4469.08</v>
       </c>
       <c r="E155" t="n">
         <v>29.34</v>
       </c>
       <c r="F155" t="n">
-        <v>16.99</v>
+        <v>16.97</v>
       </c>
       <c r="G155" t="inlineStr">
         <is>
@@ -4943,16 +4943,16 @@
         </is>
       </c>
       <c r="C156" t="n">
-        <v>293.35</v>
+        <v>293</v>
       </c>
       <c r="D156" t="n">
-        <v>4416.58</v>
+        <v>4411.31</v>
       </c>
       <c r="E156" t="n">
         <v>25.79</v>
       </c>
       <c r="F156" t="n">
-        <v>20.9</v>
+        <v>20.88</v>
       </c>
       <c r="G156" t="inlineStr">
         <is>
@@ -4972,16 +4972,16 @@
         </is>
       </c>
       <c r="C157" t="n">
-        <v>5856.45</v>
+        <v>5845.05</v>
       </c>
       <c r="D157" t="n">
-        <v>4414.14</v>
+        <v>4405.55</v>
       </c>
       <c r="E157" t="n">
         <v>17.45</v>
       </c>
       <c r="F157" t="n">
-        <v>42.35</v>
+        <v>42.27</v>
       </c>
       <c r="G157" t="inlineStr">
         <is>
@@ -5001,16 +5001,16 @@
         </is>
       </c>
       <c r="C158" t="n">
-        <v>350</v>
+        <v>343</v>
       </c>
       <c r="D158" t="n">
-        <v>4351.35</v>
+        <v>4264.32</v>
       </c>
       <c r="E158" t="n">
         <v>64.45</v>
       </c>
       <c r="F158" t="n">
-        <v>18.42</v>
+        <v>18.05</v>
       </c>
       <c r="G158" t="inlineStr">
         <is>
@@ -5030,16 +5030,16 @@
         </is>
       </c>
       <c r="C159" t="n">
-        <v>673.8</v>
+        <v>665.9</v>
       </c>
       <c r="D159" t="n">
-        <v>4312.32</v>
+        <v>4261.76</v>
       </c>
       <c r="E159" t="n">
         <v>16.47</v>
       </c>
       <c r="F159" t="n">
-        <v>10.39</v>
+        <v>10.27</v>
       </c>
       <c r="G159" t="inlineStr">
         <is>
@@ -5088,16 +5088,16 @@
         </is>
       </c>
       <c r="C161" t="n">
-        <v>289.2</v>
+        <v>288.65</v>
       </c>
       <c r="D161" t="n">
-        <v>4174.9</v>
+        <v>4166.96</v>
       </c>
       <c r="E161" t="n">
         <v>27.41</v>
       </c>
       <c r="F161" t="n">
-        <v>24.64</v>
+        <v>24.6</v>
       </c>
       <c r="G161" t="inlineStr">
         <is>
@@ -5146,16 +5146,16 @@
         </is>
       </c>
       <c r="C163" t="n">
-        <v>601.85</v>
+        <v>598</v>
       </c>
       <c r="D163" t="n">
-        <v>4046.09</v>
+        <v>4020.2</v>
       </c>
       <c r="E163" t="n">
         <v>81.98999999999999</v>
       </c>
       <c r="F163" t="n">
-        <v>10.96</v>
+        <v>10.89</v>
       </c>
       <c r="G163" t="inlineStr">
         <is>
@@ -5166,25 +5166,25 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Raymond Realty</t>
+          <t>Hawkins Cookers</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>RAYMONDREL</t>
+          <t>HAWKINCOOK</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>604.55</v>
+        <v>7580</v>
       </c>
       <c r="D164" t="n">
-        <v>4024.73</v>
+        <v>4009.81</v>
       </c>
       <c r="E164" t="n">
-        <v>29.61</v>
+        <v>40.89</v>
       </c>
       <c r="F164" t="n">
-        <v>13.37</v>
+        <v>29.56</v>
       </c>
       <c r="G164" t="inlineStr">
         <is>
@@ -5195,25 +5195,25 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Hawkins Cookers</t>
+          <t>Raymond Realty</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>HAWKINCOOK</t>
+          <t>RAYMONDREL</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>7580</v>
+        <v>598.4</v>
       </c>
       <c r="D165" t="n">
-        <v>4009.81</v>
+        <v>3983.79</v>
       </c>
       <c r="E165" t="n">
-        <v>40.89</v>
+        <v>29.61</v>
       </c>
       <c r="F165" t="n">
-        <v>29.56</v>
+        <v>13.24</v>
       </c>
       <c r="G165" t="inlineStr">
         <is>
@@ -5233,16 +5233,16 @@
         </is>
       </c>
       <c r="C166" t="n">
-        <v>140.5</v>
+        <v>140.4</v>
       </c>
       <c r="D166" t="n">
-        <v>3883.52</v>
+        <v>3880.77</v>
       </c>
       <c r="E166" t="n">
         <v>16</v>
       </c>
       <c r="F166" t="n">
-        <v>83</v>
+        <v>82.94</v>
       </c>
       <c r="G166" t="inlineStr">
         <is>
@@ -5262,16 +5262,16 @@
         </is>
       </c>
       <c r="C167" t="n">
-        <v>1092.55</v>
+        <v>1095.25</v>
       </c>
       <c r="D167" t="n">
-        <v>3860.98</v>
+        <v>3870.52</v>
       </c>
       <c r="E167" t="n">
         <v>19.92</v>
       </c>
       <c r="F167" t="n">
-        <v>20.8</v>
+        <v>20.85</v>
       </c>
       <c r="G167" t="inlineStr">
         <is>
@@ -5320,16 +5320,16 @@
         </is>
       </c>
       <c r="C169" t="n">
-        <v>567.35</v>
+        <v>566.6</v>
       </c>
       <c r="D169" t="n">
-        <v>3819.13</v>
+        <v>3814.08</v>
       </c>
       <c r="E169" t="n">
         <v>16.35</v>
       </c>
       <c r="F169" t="n">
-        <v>25.51</v>
+        <v>25.48</v>
       </c>
       <c r="G169" t="inlineStr">
         <is>
@@ -5340,25 +5340,25 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Afcom Holdings</t>
+          <t>Kwality Pharma</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>544224</t>
+          <t>KPL</t>
         </is>
       </c>
       <c r="C170" t="n">
-        <v>1300</v>
+        <v>3598.45</v>
       </c>
       <c r="D170" t="n">
-        <v>3758.75</v>
+        <v>3733.82</v>
       </c>
       <c r="E170" t="n">
-        <v>27.97</v>
+        <v>24.08</v>
       </c>
       <c r="F170" t="n">
-        <v>25.6</v>
+        <v>45.78</v>
       </c>
       <c r="G170" t="inlineStr">
         <is>
@@ -5369,25 +5369,25 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Kwality Pharma</t>
+          <t>Afcom Holdings</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>KPL</t>
+          <t>544224</t>
         </is>
       </c>
       <c r="C171" t="n">
-        <v>3600.5</v>
+        <v>1290</v>
       </c>
       <c r="D171" t="n">
-        <v>3735.95</v>
+        <v>3729.83</v>
       </c>
       <c r="E171" t="n">
-        <v>24.08</v>
+        <v>27.97</v>
       </c>
       <c r="F171" t="n">
-        <v>45.81</v>
+        <v>25.4</v>
       </c>
       <c r="G171" t="inlineStr">
         <is>
@@ -5407,16 +5407,16 @@
         </is>
       </c>
       <c r="C172" t="n">
-        <v>1792.05</v>
+        <v>1793.3</v>
       </c>
       <c r="D172" t="n">
-        <v>3712.44</v>
+        <v>3715.03</v>
       </c>
       <c r="E172" t="n">
         <v>21.27</v>
       </c>
       <c r="F172" t="n">
-        <v>35.75</v>
+        <v>35.78</v>
       </c>
       <c r="G172" t="inlineStr">
         <is>
@@ -5465,16 +5465,16 @@
         </is>
       </c>
       <c r="C174" t="n">
-        <v>122.65</v>
+        <v>121.8</v>
       </c>
       <c r="D174" t="n">
-        <v>3552.83</v>
+        <v>3528.21</v>
       </c>
       <c r="E174" t="n">
         <v>34.32</v>
       </c>
       <c r="F174" t="n">
-        <v>13.6</v>
+        <v>13.51</v>
       </c>
       <c r="G174" t="inlineStr">
         <is>
@@ -5523,16 +5523,16 @@
         </is>
       </c>
       <c r="C176" t="n">
-        <v>1677.5</v>
+        <v>1668.5</v>
       </c>
       <c r="D176" t="n">
-        <v>3499.84</v>
+        <v>3481.07</v>
       </c>
       <c r="E176" t="n">
         <v>19.71</v>
       </c>
       <c r="F176" t="n">
-        <v>78.37</v>
+        <v>77.95</v>
       </c>
       <c r="G176" t="inlineStr">
         <is>
@@ -5552,16 +5552,16 @@
         </is>
       </c>
       <c r="C177" t="n">
-        <v>516.35</v>
+        <v>517</v>
       </c>
       <c r="D177" t="n">
-        <v>3375.67</v>
+        <v>3379.92</v>
       </c>
       <c r="E177" t="n">
         <v>21.23</v>
       </c>
       <c r="F177" t="n">
-        <v>21.59</v>
+        <v>21.62</v>
       </c>
       <c r="G177" t="inlineStr">
         <is>
@@ -5581,16 +5581,16 @@
         </is>
       </c>
       <c r="C178" t="n">
-        <v>714.2</v>
+        <v>716.05</v>
       </c>
       <c r="D178" t="n">
-        <v>3225.46</v>
+        <v>3233.82</v>
       </c>
       <c r="E178" t="n">
         <v>21.59</v>
       </c>
       <c r="F178" t="n">
-        <v>17.6</v>
+        <v>17.64</v>
       </c>
       <c r="G178" t="inlineStr">
         <is>
@@ -5639,16 +5639,16 @@
         </is>
       </c>
       <c r="C180" t="n">
-        <v>71.90000000000001</v>
+        <v>71.2</v>
       </c>
       <c r="D180" t="n">
-        <v>3181.78</v>
+        <v>3150.81</v>
       </c>
       <c r="E180" t="n">
         <v>36.98</v>
       </c>
       <c r="F180" t="n">
-        <v>88.29000000000001</v>
+        <v>87.43000000000001</v>
       </c>
       <c r="G180" t="inlineStr">
         <is>
@@ -5717,25 +5717,25 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Anand Rathi Shar</t>
+          <t>Panama Petrochem</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>ARSSBL</t>
+          <t>PANAMAPET</t>
         </is>
       </c>
       <c r="C183" t="n">
-        <v>465.5</v>
+        <v>490.1</v>
       </c>
       <c r="D183" t="n">
-        <v>2937.82</v>
+        <v>2964.76</v>
       </c>
       <c r="E183" t="n">
-        <v>19.82</v>
+        <v>19.15</v>
       </c>
       <c r="F183" t="n">
-        <v>18.19</v>
+        <v>6.21</v>
       </c>
       <c r="G183" t="inlineStr">
         <is>
@@ -5746,25 +5746,25 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Panama Petrochem</t>
+          <t>Anand Rathi Shar</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>PANAMAPET</t>
+          <t>ARSSBL</t>
         </is>
       </c>
       <c r="C184" t="n">
-        <v>485</v>
+        <v>464.7</v>
       </c>
       <c r="D184" t="n">
-        <v>2933.91</v>
+        <v>2932.78</v>
       </c>
       <c r="E184" t="n">
-        <v>19.15</v>
+        <v>19.82</v>
       </c>
       <c r="F184" t="n">
-        <v>6.15</v>
+        <v>18.16</v>
       </c>
       <c r="G184" t="inlineStr">
         <is>
@@ -5813,16 +5813,16 @@
         </is>
       </c>
       <c r="C186" t="n">
-        <v>331.9</v>
+        <v>326.3</v>
       </c>
       <c r="D186" t="n">
-        <v>2873.43</v>
+        <v>2824.94</v>
       </c>
       <c r="E186" t="n">
         <v>15.63</v>
       </c>
       <c r="F186" t="n">
-        <v>14.01</v>
+        <v>13.78</v>
       </c>
       <c r="G186" t="inlineStr">
         <is>
@@ -5842,16 +5842,16 @@
         </is>
       </c>
       <c r="C187" t="n">
-        <v>342.2</v>
+        <v>339</v>
       </c>
       <c r="D187" t="n">
-        <v>2833.83</v>
+        <v>2807.34</v>
       </c>
       <c r="E187" t="n">
         <v>15.69</v>
       </c>
       <c r="F187" t="n">
-        <v>24.52</v>
+        <v>24.29</v>
       </c>
       <c r="G187" t="inlineStr">
         <is>
@@ -5871,16 +5871,16 @@
         </is>
       </c>
       <c r="C188" t="n">
-        <v>1290.5</v>
+        <v>1284</v>
       </c>
       <c r="D188" t="n">
-        <v>2805.02</v>
+        <v>2790.89</v>
       </c>
       <c r="E188" t="n">
         <v>34.79</v>
       </c>
       <c r="F188" t="n">
-        <v>79.18000000000001</v>
+        <v>78.78</v>
       </c>
       <c r="G188" t="inlineStr">
         <is>
@@ -5900,16 +5900,16 @@
         </is>
       </c>
       <c r="C189" t="n">
-        <v>1615</v>
+        <v>1623.45</v>
       </c>
       <c r="D189" t="n">
-        <v>2713.78</v>
+        <v>2727.98</v>
       </c>
       <c r="E189" t="n">
         <v>47.83</v>
       </c>
       <c r="F189" t="n">
-        <v>14.27</v>
+        <v>14.34</v>
       </c>
       <c r="G189" t="inlineStr">
         <is>
@@ -5929,16 +5929,16 @@
         </is>
       </c>
       <c r="C190" t="n">
-        <v>241.4</v>
+        <v>241</v>
       </c>
       <c r="D190" t="n">
-        <v>2652.13</v>
+        <v>2647.74</v>
       </c>
       <c r="E190" t="n">
         <v>21.82</v>
       </c>
       <c r="F190" t="n">
-        <v>27.39</v>
+        <v>27.34</v>
       </c>
       <c r="G190" t="inlineStr">
         <is>
@@ -5949,25 +5949,25 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Dr Agarwal's Eye</t>
+          <t>Crizac</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>DRAGARWQ</t>
+          <t>CRIZAC</t>
         </is>
       </c>
       <c r="C191" t="n">
-        <v>5221</v>
+        <v>144.8</v>
       </c>
       <c r="D191" t="n">
-        <v>2523.21</v>
+        <v>2533.74</v>
       </c>
       <c r="E191" t="n">
-        <v>17.19</v>
+        <v>52.34</v>
       </c>
       <c r="F191" t="n">
-        <v>33.11</v>
+        <v>11.48</v>
       </c>
       <c r="G191" t="inlineStr">
         <is>
@@ -5978,25 +5978,25 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Crizac</t>
+          <t>Dr Agarwal's Eye</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>CRIZAC</t>
+          <t>DRAGARWQ</t>
         </is>
       </c>
       <c r="C192" t="n">
-        <v>144.15</v>
+        <v>5221</v>
       </c>
       <c r="D192" t="n">
-        <v>2522.37</v>
+        <v>2523.21</v>
       </c>
       <c r="E192" t="n">
-        <v>52.34</v>
+        <v>17.19</v>
       </c>
       <c r="F192" t="n">
-        <v>11.43</v>
+        <v>33.11</v>
       </c>
       <c r="G192" t="inlineStr">
         <is>
@@ -6007,25 +6007,25 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Fredun Pharma</t>
+          <t>Amic Forging</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>FREDUN</t>
+          <t>544037</t>
         </is>
       </c>
       <c r="C193" t="n">
-        <v>1456.9</v>
+        <v>2161.9</v>
       </c>
       <c r="D193" t="n">
-        <v>2495.07</v>
+        <v>2496.75</v>
       </c>
       <c r="E193" t="n">
-        <v>21.49</v>
+        <v>25.24</v>
       </c>
       <c r="F193" t="n">
-        <v>56.12</v>
+        <v>81.94</v>
       </c>
       <c r="G193" t="inlineStr">
         <is>
@@ -6036,25 +6036,25 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>EFC (I)</t>
+          <t>Fredun Pharma</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>EFCIL</t>
+          <t>FREDUN</t>
         </is>
       </c>
       <c r="C194" t="n">
-        <v>165.4</v>
+        <v>1451.35</v>
       </c>
       <c r="D194" t="n">
-        <v>2480.12</v>
+        <v>2485.56</v>
       </c>
       <c r="E194" t="n">
-        <v>19.85</v>
+        <v>21.49</v>
       </c>
       <c r="F194" t="n">
-        <v>9.640000000000001</v>
+        <v>55.91</v>
       </c>
       <c r="G194" t="inlineStr">
         <is>
@@ -6065,25 +6065,25 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Amic Forging</t>
+          <t>EFC (I)</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>544037</t>
+          <t>EFCIL</t>
         </is>
       </c>
       <c r="C195" t="n">
-        <v>2143</v>
+        <v>165.05</v>
       </c>
       <c r="D195" t="n">
-        <v>2474.92</v>
+        <v>2474.87</v>
       </c>
       <c r="E195" t="n">
-        <v>25.24</v>
+        <v>19.85</v>
       </c>
       <c r="F195" t="n">
-        <v>81.22</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="G195" t="inlineStr">
         <is>
@@ -6094,25 +6094,25 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Kilburn Engg.</t>
+          <t>Concord Control</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>KLBRENG-B</t>
+          <t>543619</t>
         </is>
       </c>
       <c r="C196" t="n">
-        <v>440.75</v>
+        <v>2380</v>
       </c>
       <c r="D196" t="n">
-        <v>2468.22</v>
+        <v>2471.24</v>
       </c>
       <c r="E196" t="n">
-        <v>22.99</v>
+        <v>31.23</v>
       </c>
       <c r="F196" t="n">
-        <v>28.07</v>
+        <v>58.67</v>
       </c>
       <c r="G196" t="inlineStr">
         <is>
@@ -6123,25 +6123,25 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Concord Control</t>
+          <t>Kilburn Engg.</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>543619</t>
+          <t>KLBRENG-B</t>
         </is>
       </c>
       <c r="C197" t="n">
-        <v>2375</v>
+        <v>440.75</v>
       </c>
       <c r="D197" t="n">
-        <v>2466.05</v>
+        <v>2468.22</v>
       </c>
       <c r="E197" t="n">
-        <v>31.23</v>
+        <v>22.99</v>
       </c>
       <c r="F197" t="n">
-        <v>58.55</v>
+        <v>28.07</v>
       </c>
       <c r="G197" t="inlineStr">
         <is>
@@ -6161,16 +6161,16 @@
         </is>
       </c>
       <c r="C198" t="n">
-        <v>240.5</v>
+        <v>240</v>
       </c>
       <c r="D198" t="n">
-        <v>2443.37</v>
+        <v>2438.29</v>
       </c>
       <c r="E198" t="n">
         <v>39.66</v>
       </c>
       <c r="F198" t="n">
-        <v>9.68</v>
+        <v>9.66</v>
       </c>
       <c r="G198" t="inlineStr">
         <is>
@@ -6190,16 +6190,16 @@
         </is>
       </c>
       <c r="C199" t="n">
-        <v>148.6</v>
+        <v>148.55</v>
       </c>
       <c r="D199" t="n">
-        <v>2423.68</v>
+        <v>2422.86</v>
       </c>
       <c r="E199" t="n">
         <v>26.24</v>
       </c>
       <c r="F199" t="n">
-        <v>43.45</v>
+        <v>43.43</v>
       </c>
       <c r="G199" t="inlineStr">
         <is>
@@ -6219,16 +6219,16 @@
         </is>
       </c>
       <c r="C200" t="n">
-        <v>411.85</v>
+        <v>410.45</v>
       </c>
       <c r="D200" t="n">
-        <v>2339.02</v>
+        <v>2331.07</v>
       </c>
       <c r="E200" t="n">
         <v>20.28</v>
       </c>
       <c r="F200" t="n">
-        <v>34.89</v>
+        <v>34.77</v>
       </c>
       <c r="G200" t="inlineStr">
         <is>
@@ -6248,16 +6248,16 @@
         </is>
       </c>
       <c r="C201" t="n">
-        <v>155.25</v>
+        <v>154.1</v>
       </c>
       <c r="D201" t="n">
-        <v>2274.19</v>
+        <v>2257.35</v>
       </c>
       <c r="E201" t="n">
         <v>18.18</v>
       </c>
       <c r="F201" t="n">
-        <v>28.85</v>
+        <v>28.64</v>
       </c>
       <c r="G201" t="inlineStr">
         <is>
@@ -6277,16 +6277,16 @@
         </is>
       </c>
       <c r="C202" t="n">
-        <v>76.37</v>
+        <v>76.23999999999999</v>
       </c>
       <c r="D202" t="n">
-        <v>2146.76</v>
+        <v>2143.11</v>
       </c>
       <c r="E202" t="n">
         <v>31.43</v>
       </c>
       <c r="F202" t="n">
-        <v>48.02</v>
+        <v>47.94</v>
       </c>
       <c r="G202" t="inlineStr">
         <is>
@@ -6306,16 +6306,16 @@
         </is>
       </c>
       <c r="C203" t="n">
-        <v>124.7</v>
+        <v>124.5</v>
       </c>
       <c r="D203" t="n">
-        <v>2146.08</v>
+        <v>2142.64</v>
       </c>
       <c r="E203" t="n">
         <v>24.34</v>
       </c>
       <c r="F203" t="n">
-        <v>48.55</v>
+        <v>48.47</v>
       </c>
       <c r="G203" t="inlineStr">
         <is>
@@ -6326,25 +6326,25 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>GSP Crop Science</t>
+          <t>CFF Fluid</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>GSPCROP</t>
+          <t>543920</t>
         </is>
       </c>
       <c r="C204" t="n">
-        <v>454.6</v>
+        <v>1002</v>
       </c>
       <c r="D204" t="n">
-        <v>2114.72</v>
+        <v>2101.6</v>
       </c>
       <c r="E204" t="n">
-        <v>18.9</v>
+        <v>23.5</v>
       </c>
       <c r="F204" t="n">
-        <v>20.23</v>
+        <v>53.53</v>
       </c>
       <c r="G204" t="inlineStr">
         <is>
@@ -6355,25 +6355,25 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>CFF Fluid</t>
+          <t>GSP Crop Science</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>543920</t>
+          <t>GSPCROP</t>
         </is>
       </c>
       <c r="C205" t="n">
-        <v>1000.05</v>
+        <v>449.2</v>
       </c>
       <c r="D205" t="n">
-        <v>2097.51</v>
+        <v>2089.6</v>
       </c>
       <c r="E205" t="n">
-        <v>23.5</v>
+        <v>18.9</v>
       </c>
       <c r="F205" t="n">
-        <v>53.43</v>
+        <v>19.99</v>
       </c>
       <c r="G205" t="inlineStr">
         <is>
@@ -6393,16 +6393,16 @@
         </is>
       </c>
       <c r="C206" t="n">
-        <v>268.45</v>
+        <v>269.9</v>
       </c>
       <c r="D206" t="n">
-        <v>2075.06</v>
+        <v>2086.27</v>
       </c>
       <c r="E206" t="n">
         <v>71.59</v>
       </c>
       <c r="F206" t="n">
-        <v>59.29</v>
+        <v>59.61</v>
       </c>
       <c r="G206" t="inlineStr">
         <is>
@@ -6413,25 +6413,25 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>GK Energy</t>
+          <t>Thejo Engg.</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>GKENERGY</t>
+          <t>THEJO</t>
         </is>
       </c>
       <c r="C207" t="n">
-        <v>102.3</v>
+        <v>1908</v>
       </c>
       <c r="D207" t="n">
-        <v>2074.89</v>
+        <v>2069.8</v>
       </c>
       <c r="E207" t="n">
-        <v>40.87</v>
+        <v>19.35</v>
       </c>
       <c r="F207" t="n">
-        <v>9.31</v>
+        <v>35.78</v>
       </c>
       <c r="G207" t="inlineStr">
         <is>
@@ -6442,25 +6442,25 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Thejo Engg.</t>
+          <t>OBSC Perfection</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>THEJO</t>
+          <t>OBSCP</t>
         </is>
       </c>
       <c r="C208" t="n">
-        <v>1908</v>
+        <v>800</v>
       </c>
       <c r="D208" t="n">
-        <v>2069.8</v>
+        <v>2067.64</v>
       </c>
       <c r="E208" t="n">
-        <v>19.35</v>
+        <v>19.52</v>
       </c>
       <c r="F208" t="n">
-        <v>35.78</v>
+        <v>65.72</v>
       </c>
       <c r="G208" t="inlineStr">
         <is>
@@ -6471,25 +6471,25 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>OBSC Perfection</t>
+          <t>Cantabil Retail</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>OBSCP</t>
+          <t>CANTABIL</t>
         </is>
       </c>
       <c r="C209" t="n">
-        <v>800</v>
+        <v>247</v>
       </c>
       <c r="D209" t="n">
-        <v>2067.64</v>
+        <v>2065.85</v>
       </c>
       <c r="E209" t="n">
-        <v>19.52</v>
+        <v>19.37</v>
       </c>
       <c r="F209" t="n">
-        <v>65.72</v>
+        <v>21.22</v>
       </c>
       <c r="G209" t="inlineStr">
         <is>
@@ -6500,25 +6500,25 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Cantabil Retail</t>
+          <t>GK Energy</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>CANTABIL</t>
+          <t>GKENERGY</t>
         </is>
       </c>
       <c r="C210" t="n">
-        <v>247</v>
+        <v>101.5</v>
       </c>
       <c r="D210" t="n">
-        <v>2065.85</v>
+        <v>2058.66</v>
       </c>
       <c r="E210" t="n">
-        <v>19.37</v>
+        <v>40.87</v>
       </c>
       <c r="F210" t="n">
-        <v>21.22</v>
+        <v>9.24</v>
       </c>
       <c r="G210" t="inlineStr">
         <is>
@@ -6538,10 +6538,10 @@
         </is>
       </c>
       <c r="C211" t="n">
-        <v>432.25</v>
+        <v>432.1</v>
       </c>
       <c r="D211" t="n">
-        <v>2037.81</v>
+        <v>2037.1</v>
       </c>
       <c r="E211" t="n">
         <v>19.29</v>
@@ -6567,16 +6567,16 @@
         </is>
       </c>
       <c r="C212" t="n">
-        <v>1023</v>
+        <v>1023.45</v>
       </c>
       <c r="D212" t="n">
-        <v>1948.31</v>
+        <v>1949.17</v>
       </c>
       <c r="E212" t="n">
         <v>43.77</v>
       </c>
       <c r="F212" t="n">
-        <v>58.25</v>
+        <v>58.28</v>
       </c>
       <c r="G212" t="inlineStr">
         <is>
@@ -6596,16 +6596,16 @@
         </is>
       </c>
       <c r="C213" t="n">
-        <v>299.35</v>
+        <v>297.25</v>
       </c>
       <c r="D213" t="n">
-        <v>1931.05</v>
+        <v>1917.5</v>
       </c>
       <c r="E213" t="n">
         <v>16.44</v>
       </c>
       <c r="F213" t="n">
-        <v>27.75</v>
+        <v>27.55</v>
       </c>
       <c r="G213" t="inlineStr">
         <is>
@@ -6625,16 +6625,16 @@
         </is>
       </c>
       <c r="C214" t="n">
-        <v>218.15</v>
+        <v>217.45</v>
       </c>
       <c r="D214" t="n">
-        <v>1918.3</v>
+        <v>1912.14</v>
       </c>
       <c r="E214" t="n">
         <v>37.33</v>
       </c>
       <c r="F214" t="n">
-        <v>26.92</v>
+        <v>26.84</v>
       </c>
       <c r="G214" t="inlineStr">
         <is>
@@ -6645,25 +6645,25 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Macpower CNC</t>
+          <t>Technocraft Ven.</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>MACPOWER</t>
+          <t>TECHNOCRAF</t>
         </is>
       </c>
       <c r="C215" t="n">
-        <v>1903.4</v>
+        <v>480</v>
       </c>
       <c r="D215" t="n">
-        <v>1904.21</v>
+        <v>1901.08</v>
       </c>
       <c r="E215" t="n">
-        <v>29.11</v>
+        <v>30.79</v>
       </c>
       <c r="F215" t="n">
-        <v>44.26</v>
+        <v>42.52</v>
       </c>
       <c r="G215" t="inlineStr">
         <is>
@@ -6674,25 +6674,25 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Technocraft Ven.</t>
+          <t>Macpower CNC</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>TECHNOCRAF</t>
+          <t>MACPOWER</t>
         </is>
       </c>
       <c r="C216" t="n">
-        <v>480.4</v>
+        <v>1898.2</v>
       </c>
       <c r="D216" t="n">
-        <v>1902.66</v>
+        <v>1899.01</v>
       </c>
       <c r="E216" t="n">
-        <v>30.79</v>
+        <v>29.11</v>
       </c>
       <c r="F216" t="n">
-        <v>42.56</v>
+        <v>44.14</v>
       </c>
       <c r="G216" t="inlineStr">
         <is>
@@ -6703,25 +6703,25 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Valiant Commun.</t>
+          <t>GHV Infra</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>526775</t>
+          <t>505504</t>
         </is>
       </c>
       <c r="C217" t="n">
-        <v>1614.95</v>
+        <v>234</v>
       </c>
       <c r="D217" t="n">
-        <v>1888.12</v>
+        <v>1881.57</v>
       </c>
       <c r="E217" t="n">
-        <v>37.69</v>
+        <v>45.97</v>
       </c>
       <c r="F217" t="n">
-        <v>69.34999999999999</v>
+        <v>33.61</v>
       </c>
       <c r="G217" t="inlineStr">
         <is>
@@ -6732,25 +6732,25 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>GHV Infra</t>
+          <t>Valiant Commun.</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>505504</t>
+          <t>526775</t>
         </is>
       </c>
       <c r="C218" t="n">
-        <v>234</v>
+        <v>1585.15</v>
       </c>
       <c r="D218" t="n">
-        <v>1881.57</v>
+        <v>1853.28</v>
       </c>
       <c r="E218" t="n">
-        <v>45.97</v>
+        <v>37.69</v>
       </c>
       <c r="F218" t="n">
-        <v>33.61</v>
+        <v>68.06999999999999</v>
       </c>
       <c r="G218" t="inlineStr">
         <is>
@@ -6761,25 +6761,25 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>PNGS Reva Diamo.</t>
+          <t>Venus Remedies</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>PNGSREVA</t>
+          <t>VENUSREM</t>
         </is>
       </c>
       <c r="C219" t="n">
-        <v>583.7</v>
+        <v>1382.5</v>
       </c>
       <c r="D219" t="n">
-        <v>1850.25</v>
+        <v>1848</v>
       </c>
       <c r="E219" t="n">
-        <v>22</v>
+        <v>20.71</v>
       </c>
       <c r="F219" t="n">
-        <v>19.45</v>
+        <v>15.2</v>
       </c>
       <c r="G219" t="inlineStr">
         <is>
@@ -6790,25 +6790,25 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Venus Remedies</t>
+          <t>PNGS Reva Diamo.</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>VENUSREM</t>
+          <t>PNGSREVA</t>
         </is>
       </c>
       <c r="C220" t="n">
-        <v>1382.5</v>
+        <v>578.7</v>
       </c>
       <c r="D220" t="n">
-        <v>1848</v>
+        <v>1834.4</v>
       </c>
       <c r="E220" t="n">
-        <v>20.71</v>
+        <v>22</v>
       </c>
       <c r="F220" t="n">
-        <v>15.2</v>
+        <v>19.28</v>
       </c>
       <c r="G220" t="inlineStr">
         <is>
@@ -6828,16 +6828,16 @@
         </is>
       </c>
       <c r="C221" t="n">
-        <v>800.75</v>
+        <v>798.45</v>
       </c>
       <c r="D221" t="n">
-        <v>1829.47</v>
+        <v>1824.21</v>
       </c>
       <c r="E221" t="n">
         <v>17.96</v>
       </c>
       <c r="F221" t="n">
-        <v>10.57</v>
+        <v>10.54</v>
       </c>
       <c r="G221" t="inlineStr">
         <is>
@@ -6848,25 +6848,25 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Millworks Technologies</t>
+          <t>Advait Energy</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>544826</t>
+          <t>ADVAIT</t>
         </is>
       </c>
       <c r="C222" t="n">
-        <v>1028.5</v>
+        <v>1657</v>
       </c>
       <c r="D222" t="n">
-        <v>1811.67</v>
+        <v>1814.47</v>
       </c>
       <c r="E222" t="n">
-        <v>80.98999999999999</v>
+        <v>25.96</v>
       </c>
       <c r="F222" t="n">
-        <v>48.81</v>
+        <v>31.44</v>
       </c>
       <c r="G222" t="inlineStr">
         <is>
@@ -6877,25 +6877,25 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>Advait Energy</t>
+          <t>Millworks Technologies</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>ADVAIT</t>
+          <t>544826</t>
         </is>
       </c>
       <c r="C223" t="n">
-        <v>1650.05</v>
+        <v>1028.5</v>
       </c>
       <c r="D223" t="n">
-        <v>1806.86</v>
+        <v>1811.67</v>
       </c>
       <c r="E223" t="n">
-        <v>25.96</v>
+        <v>80.98999999999999</v>
       </c>
       <c r="F223" t="n">
-        <v>31.31</v>
+        <v>48.81</v>
       </c>
       <c r="G223" t="inlineStr">
         <is>
@@ -7031,16 +7031,16 @@
         </is>
       </c>
       <c r="C228" t="n">
-        <v>324.2</v>
+        <v>324.4</v>
       </c>
       <c r="D228" t="n">
-        <v>1674.41</v>
+        <v>1675.44</v>
       </c>
       <c r="E228" t="n">
         <v>22.76</v>
       </c>
       <c r="F228" t="n">
-        <v>49.4</v>
+        <v>49.43</v>
       </c>
       <c r="G228" t="inlineStr">
         <is>
@@ -7051,25 +7051,25 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>RACL Geartech</t>
+          <t>NGL Fine Chem</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>RACLGEAR</t>
+          <t>NGLFINE</t>
         </is>
       </c>
       <c r="C229" t="n">
-        <v>1398.9</v>
+        <v>2639.85</v>
       </c>
       <c r="D229" t="n">
-        <v>1649.02</v>
+        <v>1631.43</v>
       </c>
       <c r="E229" t="n">
-        <v>16.55</v>
+        <v>16.69</v>
       </c>
       <c r="F229" t="n">
-        <v>34.94</v>
+        <v>32.34</v>
       </c>
       <c r="G229" t="inlineStr">
         <is>
@@ -7080,25 +7080,25 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>NGL Fine Chem</t>
+          <t>RACL Geartech</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>NGLFINE</t>
+          <t>RACLGEAR</t>
         </is>
       </c>
       <c r="C230" t="n">
-        <v>2639.85</v>
+        <v>1380</v>
       </c>
       <c r="D230" t="n">
-        <v>1631.43</v>
+        <v>1626.74</v>
       </c>
       <c r="E230" t="n">
-        <v>16.69</v>
+        <v>16.55</v>
       </c>
       <c r="F230" t="n">
-        <v>32.34</v>
+        <v>34.47</v>
       </c>
       <c r="G230" t="inlineStr">
         <is>
@@ -7147,16 +7147,16 @@
         </is>
       </c>
       <c r="C232" t="n">
-        <v>127.9</v>
+        <v>127</v>
       </c>
       <c r="D232" t="n">
-        <v>1621.89</v>
+        <v>1610.48</v>
       </c>
       <c r="E232" t="n">
         <v>29.78</v>
       </c>
       <c r="F232" t="n">
-        <v>38.89</v>
+        <v>38.62</v>
       </c>
       <c r="G232" t="inlineStr">
         <is>
@@ -7176,16 +7176,16 @@
         </is>
       </c>
       <c r="C233" t="n">
-        <v>351.15</v>
+        <v>350.65</v>
       </c>
       <c r="D233" t="n">
-        <v>1608.55</v>
+        <v>1606.26</v>
       </c>
       <c r="E233" t="n">
         <v>32.17</v>
       </c>
       <c r="F233" t="n">
-        <v>43.94</v>
+        <v>43.88</v>
       </c>
       <c r="G233" t="inlineStr">
         <is>
@@ -7292,10 +7292,10 @@
         </is>
       </c>
       <c r="C237" t="n">
-        <v>305.05</v>
+        <v>305</v>
       </c>
       <c r="D237" t="n">
-        <v>1523.6</v>
+        <v>1523.35</v>
       </c>
       <c r="E237" t="n">
         <v>18.76</v>
@@ -7312,25 +7312,25 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Frontier Springs</t>
+          <t>Menon Bearings</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>FRONTSP</t>
+          <t>MENONBE</t>
         </is>
       </c>
       <c r="C238" t="n">
-        <v>1286.8</v>
+        <v>271.25</v>
       </c>
       <c r="D238" t="n">
-        <v>1520.45</v>
+        <v>1520.08</v>
       </c>
       <c r="E238" t="n">
-        <v>50.63</v>
+        <v>25.5</v>
       </c>
       <c r="F238" t="n">
-        <v>25.96</v>
+        <v>34.62</v>
       </c>
       <c r="G238" t="inlineStr">
         <is>
@@ -7341,25 +7341,25 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>Menon Bearings</t>
+          <t>Frontier Springs</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>MENONBE</t>
+          <t>FRONTSP</t>
         </is>
       </c>
       <c r="C239" t="n">
-        <v>271.25</v>
+        <v>1274.4</v>
       </c>
       <c r="D239" t="n">
-        <v>1520.08</v>
+        <v>1505.8</v>
       </c>
       <c r="E239" t="n">
-        <v>25.5</v>
+        <v>50.63</v>
       </c>
       <c r="F239" t="n">
-        <v>34.62</v>
+        <v>25.71</v>
       </c>
       <c r="G239" t="inlineStr">
         <is>
@@ -7408,16 +7408,16 @@
         </is>
       </c>
       <c r="C241" t="n">
-        <v>804</v>
+        <v>804.75</v>
       </c>
       <c r="D241" t="n">
-        <v>1448.5</v>
+        <v>1449.85</v>
       </c>
       <c r="E241" t="n">
         <v>22.46</v>
       </c>
       <c r="F241" t="n">
-        <v>21.65</v>
+        <v>21.67</v>
       </c>
       <c r="G241" t="inlineStr">
         <is>
@@ -7495,16 +7495,16 @@
         </is>
       </c>
       <c r="C244" t="n">
-        <v>53.01</v>
+        <v>53.03</v>
       </c>
       <c r="D244" t="n">
-        <v>1367.19</v>
+        <v>1367.71</v>
       </c>
       <c r="E244" t="n">
         <v>16.85</v>
       </c>
       <c r="F244" t="n">
-        <v>15.04</v>
+        <v>15.05</v>
       </c>
       <c r="G244" t="inlineStr">
         <is>
@@ -7524,16 +7524,16 @@
         </is>
       </c>
       <c r="C245" t="n">
-        <v>43.28</v>
+        <v>43.13</v>
       </c>
       <c r="D245" t="n">
-        <v>1364.18</v>
+        <v>1359.46</v>
       </c>
       <c r="E245" t="n">
         <v>49.08</v>
       </c>
       <c r="F245" t="n">
-        <v>15.81</v>
+        <v>15.76</v>
       </c>
       <c r="G245" t="inlineStr">
         <is>
@@ -7553,16 +7553,16 @@
         </is>
       </c>
       <c r="C246" t="n">
-        <v>1060</v>
+        <v>1051.75</v>
       </c>
       <c r="D246" t="n">
-        <v>1358.52</v>
+        <v>1347.95</v>
       </c>
       <c r="E246" t="n">
         <v>15.6</v>
       </c>
       <c r="F246" t="n">
-        <v>35.68</v>
+        <v>35.4</v>
       </c>
       <c r="G246" t="inlineStr">
         <is>
@@ -7582,16 +7582,16 @@
         </is>
       </c>
       <c r="C247" t="n">
-        <v>268</v>
+        <v>269.4</v>
       </c>
       <c r="D247" t="n">
-        <v>1340</v>
+        <v>1347</v>
       </c>
       <c r="E247" t="n">
         <v>36.43</v>
       </c>
       <c r="F247" t="n">
-        <v>9.98</v>
+        <v>10.03</v>
       </c>
       <c r="G247" t="inlineStr">
         <is>
@@ -7602,25 +7602,25 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>Indo Borax &amp; Ch.</t>
+          <t>Rajesh Power</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>INDOBORAX</t>
+          <t>544291</t>
         </is>
       </c>
       <c r="C248" t="n">
-        <v>412.55</v>
+        <v>733.25</v>
       </c>
       <c r="D248" t="n">
-        <v>1323.85</v>
+        <v>1320.39</v>
       </c>
       <c r="E248" t="n">
-        <v>15.37</v>
+        <v>47.33</v>
       </c>
       <c r="F248" t="n">
-        <v>27.04</v>
+        <v>9.59</v>
       </c>
       <c r="G248" t="inlineStr">
         <is>
@@ -7631,25 +7631,25 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>Rajesh Power</t>
+          <t>Garuda Cons</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>544291</t>
+          <t>GARUDA</t>
         </is>
       </c>
       <c r="C249" t="n">
-        <v>733.25</v>
+        <v>141.35</v>
       </c>
       <c r="D249" t="n">
-        <v>1320.39</v>
+        <v>1315.14</v>
       </c>
       <c r="E249" t="n">
-        <v>47.33</v>
+        <v>42.4</v>
       </c>
       <c r="F249" t="n">
-        <v>9.59</v>
+        <v>9.65</v>
       </c>
       <c r="G249" t="inlineStr">
         <is>
@@ -7660,25 +7660,25 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>Garuda Cons</t>
+          <t>Indo Borax &amp; Ch.</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>GARUDA</t>
+          <t>INDOBORAX</t>
         </is>
       </c>
       <c r="C250" t="n">
-        <v>140.95</v>
+        <v>409.8</v>
       </c>
       <c r="D250" t="n">
-        <v>1311.42</v>
+        <v>1315.03</v>
       </c>
       <c r="E250" t="n">
-        <v>42.4</v>
+        <v>15.37</v>
       </c>
       <c r="F250" t="n">
-        <v>9.619999999999999</v>
+        <v>26.86</v>
       </c>
       <c r="G250" t="inlineStr">
         <is>
@@ -7698,16 +7698,16 @@
         </is>
       </c>
       <c r="C251" t="n">
-        <v>841</v>
+        <v>834.95</v>
       </c>
       <c r="D251" t="n">
-        <v>1310.43</v>
+        <v>1301</v>
       </c>
       <c r="E251" t="n">
         <v>27.48</v>
       </c>
       <c r="F251" t="n">
-        <v>21.07</v>
+        <v>20.92</v>
       </c>
       <c r="G251" t="inlineStr">
         <is>
@@ -7718,25 +7718,25 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>Ceinsys Tech</t>
+          <t>Anlon Healthcare</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>CEINSYS</t>
+          <t>AHCL</t>
         </is>
       </c>
       <c r="C252" t="n">
-        <v>620.75</v>
+        <v>24.47</v>
       </c>
       <c r="D252" t="n">
-        <v>1299.71</v>
+        <v>1300.62</v>
       </c>
       <c r="E252" t="n">
-        <v>27.69</v>
+        <v>20.77</v>
       </c>
       <c r="F252" t="n">
-        <v>9.720000000000001</v>
+        <v>41.13</v>
       </c>
       <c r="G252" t="inlineStr">
         <is>
@@ -7747,25 +7747,25 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>Anlon Healthcare</t>
+          <t>Ceinsys Tech</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>AHCL</t>
+          <t>CEINSYS</t>
         </is>
       </c>
       <c r="C253" t="n">
-        <v>24.42</v>
+        <v>619</v>
       </c>
       <c r="D253" t="n">
-        <v>1297.96</v>
+        <v>1296.05</v>
       </c>
       <c r="E253" t="n">
-        <v>20.77</v>
+        <v>27.69</v>
       </c>
       <c r="F253" t="n">
-        <v>41.05</v>
+        <v>9.69</v>
       </c>
       <c r="G253" t="inlineStr">
         <is>
@@ -7785,16 +7785,16 @@
         </is>
       </c>
       <c r="C254" t="n">
-        <v>228.4</v>
+        <v>227.8</v>
       </c>
       <c r="D254" t="n">
-        <v>1220.79</v>
+        <v>1217.59</v>
       </c>
       <c r="E254" t="n">
         <v>25.13</v>
       </c>
       <c r="F254" t="n">
-        <v>16.63</v>
+        <v>16.58</v>
       </c>
       <c r="G254" t="inlineStr">
         <is>
@@ -7805,25 +7805,25 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>Airfloa Rail</t>
+          <t>Modison</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>544516</t>
+          <t>MODISONLTD</t>
         </is>
       </c>
       <c r="C255" t="n">
-        <v>501</v>
+        <v>369.55</v>
       </c>
       <c r="D255" t="n">
-        <v>1200.87</v>
+        <v>1199.2</v>
       </c>
       <c r="E255" t="n">
-        <v>25.87</v>
+        <v>30.98</v>
       </c>
       <c r="F255" t="n">
-        <v>30.65</v>
+        <v>10.25</v>
       </c>
       <c r="G255" t="inlineStr">
         <is>
@@ -7834,25 +7834,25 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>Modison</t>
+          <t>Airfloa Rail</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>MODISONLTD</t>
+          <t>544516</t>
         </is>
       </c>
       <c r="C256" t="n">
-        <v>369.55</v>
+        <v>497.05</v>
       </c>
       <c r="D256" t="n">
-        <v>1199.2</v>
+        <v>1191.4</v>
       </c>
       <c r="E256" t="n">
-        <v>30.98</v>
+        <v>25.87</v>
       </c>
       <c r="F256" t="n">
-        <v>10.25</v>
+        <v>30.41</v>
       </c>
       <c r="G256" t="inlineStr">
         <is>
@@ -7921,25 +7921,25 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>K.P. Energy</t>
+          <t>Vikram Thermo</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>KPEL</t>
+          <t>530477</t>
         </is>
       </c>
       <c r="C259" t="n">
-        <v>166.15</v>
+        <v>359.55</v>
       </c>
       <c r="D259" t="n">
-        <v>1126.46</v>
+        <v>1127.47</v>
       </c>
       <c r="E259" t="n">
-        <v>39</v>
+        <v>36.19</v>
       </c>
       <c r="F259" t="n">
-        <v>6.19</v>
+        <v>25.74</v>
       </c>
       <c r="G259" t="inlineStr">
         <is>
@@ -7950,25 +7950,25 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>Vikram Thermo</t>
+          <t>K.P. Energy</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>530477</t>
+          <t>KPEL</t>
         </is>
       </c>
       <c r="C260" t="n">
-        <v>354.5</v>
+        <v>165.5</v>
       </c>
       <c r="D260" t="n">
-        <v>1111.64</v>
+        <v>1122.05</v>
       </c>
       <c r="E260" t="n">
-        <v>36.19</v>
+        <v>39</v>
       </c>
       <c r="F260" t="n">
-        <v>25.38</v>
+        <v>6.18</v>
       </c>
       <c r="G260" t="inlineStr">
         <is>
@@ -8017,16 +8017,16 @@
         </is>
       </c>
       <c r="C262" t="n">
-        <v>56.72</v>
+        <v>57.41</v>
       </c>
       <c r="D262" t="n">
-        <v>1079.57</v>
+        <v>1092.71</v>
       </c>
       <c r="E262" t="n">
         <v>16.04</v>
       </c>
       <c r="F262" t="n">
-        <v>61.45</v>
+        <v>62.19</v>
       </c>
       <c r="G262" t="inlineStr">
         <is>
@@ -8104,16 +8104,16 @@
         </is>
       </c>
       <c r="C265" t="n">
-        <v>192.75</v>
+        <v>192.9</v>
       </c>
       <c r="D265" t="n">
-        <v>1015.03</v>
+        <v>1015.82</v>
       </c>
       <c r="E265" t="n">
         <v>30.7</v>
       </c>
       <c r="F265" t="n">
-        <v>9.699999999999999</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="G265" t="inlineStr">
         <is>
@@ -8133,16 +8133,16 @@
         </is>
       </c>
       <c r="C266" t="n">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="D266" t="n">
-        <v>1003.61</v>
+        <v>1010.53</v>
       </c>
       <c r="E266" t="n">
         <v>32.47</v>
       </c>
       <c r="F266" t="n">
-        <v>16.52</v>
+        <v>16.63</v>
       </c>
       <c r="G266" t="inlineStr">
         <is>
@@ -8162,16 +8162,16 @@
         </is>
       </c>
       <c r="C267" t="n">
-        <v>24.87</v>
+        <v>24.81</v>
       </c>
       <c r="D267" t="n">
-        <v>990.02</v>
+        <v>987.63</v>
       </c>
       <c r="E267" t="n">
         <v>17.52</v>
       </c>
       <c r="F267" t="n">
-        <v>58.52</v>
+        <v>58.38</v>
       </c>
       <c r="G267" t="inlineStr">
         <is>
@@ -8191,16 +8191,16 @@
         </is>
       </c>
       <c r="C268" t="n">
-        <v>179.2</v>
+        <v>178.8</v>
       </c>
       <c r="D268" t="n">
-        <v>986.16</v>
+        <v>983.96</v>
       </c>
       <c r="E268" t="n">
         <v>15.05</v>
       </c>
       <c r="F268" t="n">
-        <v>28.32</v>
+        <v>28.25</v>
       </c>
       <c r="G268" t="inlineStr">
         <is>
@@ -8220,16 +8220,16 @@
         </is>
       </c>
       <c r="C269" t="n">
-        <v>53.12</v>
+        <v>53</v>
       </c>
       <c r="D269" t="n">
-        <v>985.1</v>
+        <v>982.87</v>
       </c>
       <c r="E269" t="n">
         <v>22.84</v>
       </c>
       <c r="F269" t="n">
-        <v>9.630000000000001</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="G269" t="inlineStr">
         <is>
@@ -8249,16 +8249,16 @@
         </is>
       </c>
       <c r="C270" t="n">
-        <v>425</v>
+        <v>428.9</v>
       </c>
       <c r="D270" t="n">
-        <v>971.34</v>
+        <v>980.25</v>
       </c>
       <c r="E270" t="n">
         <v>33.78</v>
       </c>
       <c r="F270" t="n">
-        <v>30</v>
+        <v>30.28</v>
       </c>
       <c r="G270" t="inlineStr">
         <is>
@@ -8269,25 +8269,25 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>Pranav Construc.</t>
+          <t>Premier Polyfilm</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>PRANAV</t>
+          <t>PREMIERPOL</t>
         </is>
       </c>
       <c r="C271" t="n">
-        <v>85.78</v>
+        <v>92.22</v>
       </c>
       <c r="D271" t="n">
-        <v>966.0700000000001</v>
+        <v>965.97</v>
       </c>
       <c r="E271" t="n">
-        <v>28.48</v>
+        <v>28.86</v>
       </c>
       <c r="F271" t="n">
-        <v>12.77</v>
+        <v>26.27</v>
       </c>
       <c r="G271" t="inlineStr">
         <is>
@@ -8298,25 +8298,25 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>Premier Polyfilm</t>
+          <t>Shree Vasu Logis</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>PREMIERPOL</t>
+          <t>SVLL</t>
         </is>
       </c>
       <c r="C272" t="n">
-        <v>92.22</v>
+        <v>840</v>
       </c>
       <c r="D272" t="n">
-        <v>965.97</v>
+        <v>965.48</v>
       </c>
       <c r="E272" t="n">
-        <v>28.86</v>
+        <v>20.48</v>
       </c>
       <c r="F272" t="n">
-        <v>26.27</v>
+        <v>134.84</v>
       </c>
       <c r="G272" t="inlineStr">
         <is>
@@ -8327,25 +8327,25 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>Shree Vasu Logis</t>
+          <t>Pranav Construc.</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>SVLL</t>
+          <t>PRANAV</t>
         </is>
       </c>
       <c r="C273" t="n">
-        <v>840</v>
+        <v>85.69</v>
       </c>
       <c r="D273" t="n">
-        <v>965.48</v>
+        <v>965.0599999999999</v>
       </c>
       <c r="E273" t="n">
-        <v>20.48</v>
+        <v>28.48</v>
       </c>
       <c r="F273" t="n">
-        <v>134.84</v>
+        <v>12.75</v>
       </c>
       <c r="G273" t="inlineStr">
         <is>
@@ -8385,25 +8385,25 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>Sathlokhar Sys.</t>
+          <t>B-Right Real</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>SSEGL</t>
+          <t>543543</t>
         </is>
       </c>
       <c r="C275" t="n">
-        <v>365</v>
+        <v>916.2</v>
       </c>
       <c r="D275" t="n">
-        <v>948.22</v>
+        <v>946.54</v>
       </c>
       <c r="E275" t="n">
-        <v>36.27</v>
+        <v>21.57</v>
       </c>
       <c r="F275" t="n">
-        <v>9.24</v>
+        <v>27.39</v>
       </c>
       <c r="G275" t="inlineStr">
         <is>
@@ -8414,25 +8414,25 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>B-Right Real</t>
+          <t>Tankup Engi.</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>543543</t>
+          <t>TANKUP</t>
         </is>
       </c>
       <c r="C276" t="n">
-        <v>916.2</v>
+        <v>1758.75</v>
       </c>
       <c r="D276" t="n">
-        <v>946.54</v>
+        <v>931.26</v>
       </c>
       <c r="E276" t="n">
-        <v>21.57</v>
+        <v>18.96</v>
       </c>
       <c r="F276" t="n">
-        <v>27.39</v>
+        <v>194.82</v>
       </c>
       <c r="G276" t="inlineStr">
         <is>
@@ -8443,25 +8443,25 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>Tankup Engi.</t>
+          <t>Jindal Poly Inve</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>TANKUP</t>
+          <t>JPOLYINVST</t>
         </is>
       </c>
       <c r="C277" t="n">
-        <v>1758.75</v>
+        <v>885.15</v>
       </c>
       <c r="D277" t="n">
-        <v>931.26</v>
+        <v>930.3</v>
       </c>
       <c r="E277" t="n">
-        <v>18.96</v>
+        <v>63.42</v>
       </c>
       <c r="F277" t="n">
-        <v>194.82</v>
+        <v>1.15</v>
       </c>
       <c r="G277" t="inlineStr">
         <is>
@@ -8472,25 +8472,25 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>Jindal Poly Inve</t>
+          <t>Sathlokhar Sys.</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>JPOLYINVST</t>
+          <t>SSEGL</t>
         </is>
       </c>
       <c r="C278" t="n">
-        <v>885.15</v>
+        <v>358</v>
       </c>
       <c r="D278" t="n">
-        <v>930.3</v>
+        <v>930.03</v>
       </c>
       <c r="E278" t="n">
-        <v>63.42</v>
+        <v>36.27</v>
       </c>
       <c r="F278" t="n">
-        <v>1.15</v>
+        <v>9.06</v>
       </c>
       <c r="G278" t="inlineStr">
         <is>
@@ -8501,25 +8501,25 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>Sahana Systems</t>
+          <t>Arih.Found.Hsg.</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>SAHANA</t>
+          <t>ARIHANT</t>
         </is>
       </c>
       <c r="C279" t="n">
-        <v>876</v>
+        <v>854.95</v>
       </c>
       <c r="D279" t="n">
-        <v>928.97</v>
+        <v>928.6900000000001</v>
       </c>
       <c r="E279" t="n">
-        <v>39.82</v>
+        <v>16.36</v>
       </c>
       <c r="F279" t="n">
-        <v>13.69</v>
+        <v>13.59</v>
       </c>
       <c r="G279" t="inlineStr">
         <is>
@@ -8530,25 +8530,25 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>Arih.Found.Hsg.</t>
+          <t>Sahana Systems</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>ARIHANT</t>
+          <t>SAHANA</t>
         </is>
       </c>
       <c r="C280" t="n">
-        <v>854.95</v>
+        <v>874.35</v>
       </c>
       <c r="D280" t="n">
-        <v>928.6900000000001</v>
+        <v>927.22</v>
       </c>
       <c r="E280" t="n">
-        <v>16.36</v>
+        <v>39.82</v>
       </c>
       <c r="F280" t="n">
-        <v>13.59</v>
+        <v>13.67</v>
       </c>
       <c r="G280" t="inlineStr">
         <is>
@@ -8713,16 +8713,16 @@
         </is>
       </c>
       <c r="C286" t="n">
-        <v>384</v>
+        <v>383.9</v>
       </c>
       <c r="D286" t="n">
-        <v>859.1</v>
+        <v>858.88</v>
       </c>
       <c r="E286" t="n">
         <v>35.67</v>
       </c>
       <c r="F286" t="n">
-        <v>30.31</v>
+        <v>30.3</v>
       </c>
       <c r="G286" t="inlineStr">
         <is>
@@ -8887,16 +8887,16 @@
         </is>
       </c>
       <c r="C292" t="n">
-        <v>370</v>
+        <v>370.4</v>
       </c>
       <c r="D292" t="n">
-        <v>778.01</v>
+        <v>778.85</v>
       </c>
       <c r="E292" t="n">
         <v>40.25</v>
       </c>
       <c r="F292" t="n">
-        <v>27.04</v>
+        <v>27.07</v>
       </c>
       <c r="G292" t="inlineStr">
         <is>
@@ -8936,25 +8936,25 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>Exhicon Events</t>
+          <t>Effwa Infra</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>543895</t>
+          <t>EFFWA</t>
         </is>
       </c>
       <c r="C294" t="n">
-        <v>468</v>
+        <v>333</v>
       </c>
       <c r="D294" t="n">
-        <v>767.4</v>
+        <v>770.8</v>
       </c>
       <c r="E294" t="n">
-        <v>29.6</v>
+        <v>29.26</v>
       </c>
       <c r="F294" t="n">
-        <v>18.87</v>
+        <v>26.93</v>
       </c>
       <c r="G294" t="inlineStr">
         <is>
@@ -8965,25 +8965,25 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>Effwa Infra</t>
+          <t>Exhicon Events</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>EFFWA</t>
+          <t>543895</t>
         </is>
       </c>
       <c r="C295" t="n">
-        <v>329</v>
+        <v>468</v>
       </c>
       <c r="D295" t="n">
-        <v>761.54</v>
+        <v>767.4</v>
       </c>
       <c r="E295" t="n">
-        <v>29.26</v>
+        <v>29.6</v>
       </c>
       <c r="F295" t="n">
-        <v>26.61</v>
+        <v>18.87</v>
       </c>
       <c r="G295" t="inlineStr">
         <is>
@@ -9023,25 +9023,25 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>Hy-Tech Engineer</t>
+          <t>IIRM Holdings</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>HTEL</t>
+          <t>IIRM</t>
         </is>
       </c>
       <c r="C297" t="n">
-        <v>77.83</v>
+        <v>105.85</v>
       </c>
       <c r="D297" t="n">
-        <v>738.25</v>
+        <v>737.8200000000001</v>
       </c>
       <c r="E297" t="n">
-        <v>23.91</v>
+        <v>20.36</v>
       </c>
       <c r="F297" t="n">
-        <v>32.17</v>
+        <v>30.01</v>
       </c>
       <c r="G297" t="inlineStr">
         <is>
@@ -9052,25 +9052,25 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>IIRM Holdings</t>
+          <t>Hy-Tech Engineer</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>IIRM</t>
+          <t>HTEL</t>
         </is>
       </c>
       <c r="C298" t="n">
-        <v>105.75</v>
+        <v>77.58</v>
       </c>
       <c r="D298" t="n">
-        <v>737.12</v>
+        <v>735.88</v>
       </c>
       <c r="E298" t="n">
-        <v>20.36</v>
+        <v>23.91</v>
       </c>
       <c r="F298" t="n">
-        <v>29.98</v>
+        <v>32.06</v>
       </c>
       <c r="G298" t="inlineStr">
         <is>
@@ -9119,16 +9119,16 @@
         </is>
       </c>
       <c r="C300" t="n">
-        <v>715</v>
+        <v>719.15</v>
       </c>
       <c r="D300" t="n">
-        <v>723.92</v>
+        <v>728.12</v>
       </c>
       <c r="E300" t="n">
         <v>51.22</v>
       </c>
       <c r="F300" t="n">
-        <v>13.18</v>
+        <v>13.27</v>
       </c>
       <c r="G300" t="inlineStr">
         <is>
@@ -9148,16 +9148,16 @@
         </is>
       </c>
       <c r="C301" t="n">
-        <v>98.55</v>
+        <v>98.5</v>
       </c>
       <c r="D301" t="n">
-        <v>717.3099999999999</v>
+        <v>716.95</v>
       </c>
       <c r="E301" t="n">
         <v>29.54</v>
       </c>
       <c r="F301" t="n">
-        <v>30.98</v>
+        <v>30.97</v>
       </c>
       <c r="G301" t="inlineStr">
         <is>
@@ -9197,25 +9197,25 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>Technocrats Plasma</t>
+          <t>Radhika Jeweltec</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>544877</t>
+          <t>RADHIKAJWE</t>
         </is>
       </c>
       <c r="C303" t="n">
-        <v>408.8</v>
+        <v>60.7</v>
       </c>
       <c r="D303" t="n">
-        <v>715.4</v>
+        <v>716.24</v>
       </c>
       <c r="E303" t="n">
-        <v>66.98</v>
+        <v>25.04</v>
       </c>
       <c r="F303" t="n">
-        <v>47.91</v>
+        <v>9.06</v>
       </c>
       <c r="G303" t="inlineStr">
         <is>
@@ -9226,25 +9226,25 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>Radhika Jeweltec</t>
+          <t>Technocrats Plasma</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>RADHIKAJWE</t>
+          <t>544877</t>
         </is>
       </c>
       <c r="C304" t="n">
-        <v>60.6</v>
+        <v>408.8</v>
       </c>
       <c r="D304" t="n">
-        <v>715.0599999999999</v>
+        <v>715.4</v>
       </c>
       <c r="E304" t="n">
-        <v>25.04</v>
+        <v>66.98</v>
       </c>
       <c r="F304" t="n">
-        <v>9.039999999999999</v>
+        <v>47.91</v>
       </c>
       <c r="G304" t="inlineStr">
         <is>
@@ -9264,16 +9264,16 @@
         </is>
       </c>
       <c r="C305" t="n">
-        <v>58.14</v>
+        <v>58.01</v>
       </c>
       <c r="D305" t="n">
-        <v>714.64</v>
+        <v>713.04</v>
       </c>
       <c r="E305" t="n">
         <v>22.21</v>
       </c>
       <c r="F305" t="n">
-        <v>18.1</v>
+        <v>18.06</v>
       </c>
       <c r="G305" t="inlineStr">
         <is>
@@ -9322,16 +9322,16 @@
         </is>
       </c>
       <c r="C307" t="n">
-        <v>16.49</v>
+        <v>16.47</v>
       </c>
       <c r="D307" t="n">
-        <v>706.13</v>
+        <v>705.27</v>
       </c>
       <c r="E307" t="n">
         <v>38.34</v>
       </c>
       <c r="F307" t="n">
-        <v>20.06</v>
+        <v>20.04</v>
       </c>
       <c r="G307" t="inlineStr">
         <is>
@@ -9371,25 +9371,25 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>Supreme Power</t>
+          <t>Prostarm Info</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>SUPREMEPWR</t>
+          <t>PROSTARM</t>
         </is>
       </c>
       <c r="C309" t="n">
-        <v>278</v>
+        <v>118.3</v>
       </c>
       <c r="D309" t="n">
-        <v>694.75</v>
+        <v>696.5</v>
       </c>
       <c r="E309" t="n">
-        <v>21.51</v>
+        <v>17.88</v>
       </c>
       <c r="F309" t="n">
-        <v>28.15</v>
+        <v>18.21</v>
       </c>
       <c r="G309" t="inlineStr">
         <is>
@@ -9400,25 +9400,25 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>Prostarm Info</t>
+          <t>RBZ Jewellers Lt</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>PROSTARM</t>
+          <t>RBZJEWEL</t>
         </is>
       </c>
       <c r="C310" t="n">
-        <v>118</v>
+        <v>173.3</v>
       </c>
       <c r="D310" t="n">
-        <v>694.73</v>
+        <v>693.2</v>
       </c>
       <c r="E310" t="n">
-        <v>17.88</v>
+        <v>21.98</v>
       </c>
       <c r="F310" t="n">
-        <v>18.16</v>
+        <v>12.22</v>
       </c>
       <c r="G310" t="inlineStr">
         <is>
@@ -9429,25 +9429,25 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>RBZ Jewellers Lt</t>
+          <t>Supreme Power</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>RBZJEWEL</t>
+          <t>SUPREMEPWR</t>
         </is>
       </c>
       <c r="C311" t="n">
-        <v>173.3</v>
+        <v>277.05</v>
       </c>
       <c r="D311" t="n">
-        <v>693.2</v>
+        <v>692.38</v>
       </c>
       <c r="E311" t="n">
-        <v>21.98</v>
+        <v>21.51</v>
       </c>
       <c r="F311" t="n">
-        <v>12.22</v>
+        <v>28.05</v>
       </c>
       <c r="G311" t="inlineStr">
         <is>
@@ -9458,25 +9458,25 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>L. T. Elevator</t>
+          <t>B C C Fuba India</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>544518</t>
+          <t>517246</t>
         </is>
       </c>
       <c r="C312" t="n">
-        <v>317</v>
+        <v>281</v>
       </c>
       <c r="D312" t="n">
-        <v>688.63</v>
+        <v>683.8</v>
       </c>
       <c r="E312" t="n">
-        <v>30.38</v>
+        <v>19.19</v>
       </c>
       <c r="F312" t="n">
-        <v>40.48</v>
+        <v>81.09</v>
       </c>
       <c r="G312" t="inlineStr">
         <is>
@@ -9487,25 +9487,25 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>B C C Fuba India</t>
+          <t>L. T. Elevator</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>517246</t>
+          <t>544518</t>
         </is>
       </c>
       <c r="C313" t="n">
-        <v>281</v>
+        <v>314.1</v>
       </c>
       <c r="D313" t="n">
-        <v>683.8</v>
+        <v>682.33</v>
       </c>
       <c r="E313" t="n">
-        <v>19.19</v>
+        <v>30.38</v>
       </c>
       <c r="F313" t="n">
-        <v>81.09</v>
+        <v>40.11</v>
       </c>
       <c r="G313" t="inlineStr">
         <is>
@@ -9554,16 +9554,16 @@
         </is>
       </c>
       <c r="C315" t="n">
-        <v>196.05</v>
+        <v>196.55</v>
       </c>
       <c r="D315" t="n">
-        <v>668.92</v>
+        <v>670.63</v>
       </c>
       <c r="E315" t="n">
         <v>31.44</v>
       </c>
       <c r="F315" t="n">
-        <v>13.73</v>
+        <v>13.77</v>
       </c>
       <c r="G315" t="inlineStr">
         <is>
@@ -9583,16 +9583,16 @@
         </is>
       </c>
       <c r="C316" t="n">
-        <v>100.9</v>
+        <v>101</v>
       </c>
       <c r="D316" t="n">
-        <v>648.5700000000001</v>
+        <v>649.22</v>
       </c>
       <c r="E316" t="n">
         <v>34.84</v>
       </c>
       <c r="F316" t="n">
-        <v>15.26</v>
+        <v>15.27</v>
       </c>
       <c r="G316" t="inlineStr">
         <is>
@@ -9641,10 +9641,10 @@
         </is>
       </c>
       <c r="C318" t="n">
-        <v>71.97</v>
+        <v>72.04000000000001</v>
       </c>
       <c r="D318" t="n">
-        <v>641.45</v>
+        <v>642.0700000000001</v>
       </c>
       <c r="E318" t="n">
         <v>21.15</v>
@@ -9699,16 +9699,16 @@
         </is>
       </c>
       <c r="C320" t="n">
-        <v>264.85</v>
+        <v>268</v>
       </c>
       <c r="D320" t="n">
-        <v>618.1</v>
+        <v>625.45</v>
       </c>
       <c r="E320" t="n">
         <v>18.25</v>
       </c>
       <c r="F320" t="n">
-        <v>54.56</v>
+        <v>55.21</v>
       </c>
       <c r="G320" t="inlineStr">
         <is>
@@ -9777,25 +9777,25 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>Influx Health.</t>
+          <t>South West Pinn.</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>INFLUX</t>
+          <t>SOUTHWEST</t>
         </is>
       </c>
       <c r="C323" t="n">
-        <v>258</v>
+        <v>181.75</v>
       </c>
       <c r="D323" t="n">
-        <v>597.28</v>
+        <v>593.48</v>
       </c>
       <c r="E323" t="n">
-        <v>38.36</v>
+        <v>20.06</v>
       </c>
       <c r="F323" t="n">
-        <v>31.24</v>
+        <v>14.82</v>
       </c>
       <c r="G323" t="inlineStr">
         <is>
@@ -9806,25 +9806,25 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>South West Pinn.</t>
+          <t>Simca Advertis.</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>SOUTHWEST</t>
+          <t>SIMCA</t>
         </is>
       </c>
       <c r="C324" t="n">
-        <v>181.75</v>
+        <v>493</v>
       </c>
       <c r="D324" t="n">
-        <v>593.48</v>
+        <v>590.1900000000001</v>
       </c>
       <c r="E324" t="n">
-        <v>20.06</v>
+        <v>109.69</v>
       </c>
       <c r="F324" t="n">
-        <v>14.82</v>
+        <v>27.84</v>
       </c>
       <c r="G324" t="inlineStr">
         <is>
@@ -9864,25 +9864,25 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>Simca Advertis.</t>
+          <t>Influx Health.</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>SIMCA</t>
+          <t>INFLUX</t>
         </is>
       </c>
       <c r="C326" t="n">
-        <v>490</v>
+        <v>250</v>
       </c>
       <c r="D326" t="n">
-        <v>586.6</v>
+        <v>578.76</v>
       </c>
       <c r="E326" t="n">
-        <v>109.69</v>
+        <v>38.36</v>
       </c>
       <c r="F326" t="n">
-        <v>27.67</v>
+        <v>30.28</v>
       </c>
       <c r="G326" t="inlineStr">
         <is>
@@ -9951,25 +9951,25 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>Sonaselection India</t>
+          <t>Sugs Lloyd</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>SONA</t>
+          <t>544501</t>
         </is>
       </c>
       <c r="C329" t="n">
-        <v>99.36</v>
+        <v>243.9</v>
       </c>
       <c r="D329" t="n">
-        <v>564.64</v>
+        <v>566.1900000000001</v>
       </c>
       <c r="E329" t="n">
-        <v>23.61</v>
+        <v>29.06</v>
       </c>
       <c r="F329" t="n">
-        <v>14.56</v>
+        <v>18.63</v>
       </c>
       <c r="G329" t="inlineStr">
         <is>
@@ -9980,25 +9980,25 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>Sugs Lloyd</t>
+          <t>Sonaselection India</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>544501</t>
+          <t>SONA</t>
         </is>
       </c>
       <c r="C330" t="n">
-        <v>242</v>
+        <v>99.36</v>
       </c>
       <c r="D330" t="n">
-        <v>561.78</v>
+        <v>564.64</v>
       </c>
       <c r="E330" t="n">
-        <v>29.06</v>
+        <v>23.61</v>
       </c>
       <c r="F330" t="n">
-        <v>18.48</v>
+        <v>14.56</v>
       </c>
       <c r="G330" t="inlineStr">
         <is>
@@ -10154,25 +10154,25 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>Msafe Equipments</t>
+          <t>PNGS Gargi FJ</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>544695</t>
+          <t>543709</t>
         </is>
       </c>
       <c r="C336" t="n">
-        <v>260</v>
+        <v>508.95</v>
       </c>
       <c r="D336" t="n">
-        <v>530.4</v>
+        <v>532.87</v>
       </c>
       <c r="E336" t="n">
-        <v>37.21</v>
+        <v>33.76</v>
       </c>
       <c r="F336" t="n">
-        <v>19.89</v>
+        <v>17.12</v>
       </c>
       <c r="G336" t="inlineStr">
         <is>
@@ -10183,25 +10183,25 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>PNGS Gargi FJ</t>
+          <t>Msafe Equipments</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>543709</t>
+          <t>544695</t>
         </is>
       </c>
       <c r="C337" t="n">
-        <v>502.05</v>
+        <v>260</v>
       </c>
       <c r="D337" t="n">
-        <v>525.65</v>
+        <v>530.4</v>
       </c>
       <c r="E337" t="n">
-        <v>33.76</v>
+        <v>37.21</v>
       </c>
       <c r="F337" t="n">
-        <v>16.89</v>
+        <v>19.89</v>
       </c>
       <c r="G337" t="inlineStr">
         <is>
@@ -10221,10 +10221,10 @@
         </is>
       </c>
       <c r="C338" t="n">
-        <v>919</v>
+        <v>918.9</v>
       </c>
       <c r="D338" t="n">
-        <v>522.55</v>
+        <v>522.49</v>
       </c>
       <c r="E338" t="n">
         <v>71.73</v>
@@ -10270,25 +10270,25 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>Cryogenic OGS</t>
+          <t>Intl. Conveyors</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>544440</t>
+          <t>INTLCONV</t>
         </is>
       </c>
       <c r="C340" t="n">
-        <v>356.5</v>
+        <v>80.48999999999999</v>
       </c>
       <c r="D340" t="n">
-        <v>509.07</v>
+        <v>513.38</v>
       </c>
       <c r="E340" t="n">
-        <v>29.56</v>
+        <v>22.04</v>
       </c>
       <c r="F340" t="n">
-        <v>59.05</v>
+        <v>3.76</v>
       </c>
       <c r="G340" t="inlineStr">
         <is>
@@ -10299,25 +10299,25 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>Intl. Conveyors</t>
+          <t>Cryogenic OGS</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>INTLCONV</t>
+          <t>544440</t>
         </is>
       </c>
       <c r="C341" t="n">
-        <v>79.81</v>
+        <v>356.5</v>
       </c>
       <c r="D341" t="n">
-        <v>509.04</v>
+        <v>509.07</v>
       </c>
       <c r="E341" t="n">
-        <v>22.04</v>
+        <v>29.56</v>
       </c>
       <c r="F341" t="n">
-        <v>3.73</v>
+        <v>59.05</v>
       </c>
       <c r="G341" t="inlineStr">
         <is>
@@ -10473,25 +10473,25 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>GP Eco Solutions</t>
+          <t>KRM Ayurveda</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>GPECO</t>
+          <t>KRMAYURVED</t>
         </is>
       </c>
       <c r="C347" t="n">
-        <v>395.9</v>
+        <v>229.5</v>
       </c>
       <c r="D347" t="n">
-        <v>488.16</v>
+        <v>487.93</v>
       </c>
       <c r="E347" t="n">
-        <v>38.74</v>
+        <v>35.31</v>
       </c>
       <c r="F347" t="n">
-        <v>12.16</v>
+        <v>19.38</v>
       </c>
       <c r="G347" t="inlineStr">
         <is>
@@ -10502,25 +10502,25 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>KRM Ayurveda</t>
+          <t>Paradeep Pari.</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>KRMAYURVED</t>
+          <t>544383</t>
         </is>
       </c>
       <c r="C348" t="n">
-        <v>229.5</v>
+        <v>303</v>
       </c>
       <c r="D348" t="n">
-        <v>487.93</v>
+        <v>482.32</v>
       </c>
       <c r="E348" t="n">
-        <v>35.31</v>
+        <v>22.19</v>
       </c>
       <c r="F348" t="n">
-        <v>19.38</v>
+        <v>15.66</v>
       </c>
       <c r="G348" t="inlineStr">
         <is>
@@ -10531,25 +10531,25 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>Paradeep Pari.</t>
+          <t>GP Eco Solutions</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>544383</t>
+          <t>GPECO</t>
         </is>
       </c>
       <c r="C349" t="n">
-        <v>303</v>
+        <v>391.15</v>
       </c>
       <c r="D349" t="n">
-        <v>482.32</v>
+        <v>482.3</v>
       </c>
       <c r="E349" t="n">
-        <v>22.19</v>
+        <v>38.74</v>
       </c>
       <c r="F349" t="n">
-        <v>15.66</v>
+        <v>12.01</v>
       </c>
       <c r="G349" t="inlineStr">
         <is>
@@ -10569,16 +10569,16 @@
         </is>
       </c>
       <c r="C350" t="n">
-        <v>117</v>
+        <v>116.9</v>
       </c>
       <c r="D350" t="n">
-        <v>479.69</v>
+        <v>479.27</v>
       </c>
       <c r="E350" t="n">
         <v>24.28</v>
       </c>
       <c r="F350" t="n">
-        <v>19.94</v>
+        <v>19.92</v>
       </c>
       <c r="G350" t="inlineStr">
         <is>
@@ -10714,16 +10714,16 @@
         </is>
       </c>
       <c r="C355" t="n">
-        <v>382</v>
+        <v>382.1</v>
       </c>
       <c r="D355" t="n">
-        <v>458.51</v>
+        <v>458.63</v>
       </c>
       <c r="E355" t="n">
         <v>24.9</v>
       </c>
       <c r="F355" t="n">
-        <v>20.32</v>
+        <v>20.33</v>
       </c>
       <c r="G355" t="inlineStr">
         <is>
@@ -10772,16 +10772,16 @@
         </is>
       </c>
       <c r="C357" t="n">
-        <v>147.75</v>
+        <v>150.6</v>
       </c>
       <c r="D357" t="n">
-        <v>442.91</v>
+        <v>451.45</v>
       </c>
       <c r="E357" t="n">
         <v>41.17</v>
       </c>
       <c r="F357" t="n">
-        <v>38.21</v>
+        <v>38.95</v>
       </c>
       <c r="G357" t="inlineStr">
         <is>
@@ -10801,16 +10801,16 @@
         </is>
       </c>
       <c r="C358" t="n">
-        <v>128.7</v>
+        <v>128</v>
       </c>
       <c r="D358" t="n">
-        <v>440.75</v>
+        <v>438.35</v>
       </c>
       <c r="E358" t="n">
         <v>42.7</v>
       </c>
       <c r="F358" t="n">
-        <v>10.45</v>
+        <v>10.39</v>
       </c>
       <c r="G358" t="inlineStr">
         <is>
@@ -10830,16 +10830,16 @@
         </is>
       </c>
       <c r="C359" t="n">
-        <v>225.5</v>
+        <v>225</v>
       </c>
       <c r="D359" t="n">
-        <v>430.7</v>
+        <v>429.75</v>
       </c>
       <c r="E359" t="n">
         <v>43.55</v>
       </c>
       <c r="F359" t="n">
-        <v>16.64</v>
+        <v>16.6</v>
       </c>
       <c r="G359" t="inlineStr">
         <is>
@@ -10917,10 +10917,10 @@
         </is>
       </c>
       <c r="C362" t="n">
-        <v>210.95</v>
+        <v>210.9</v>
       </c>
       <c r="D362" t="n">
-        <v>425.25</v>
+        <v>425.15</v>
       </c>
       <c r="E362" t="n">
         <v>56.08</v>
@@ -10966,25 +10966,25 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>Sotefin Bharat</t>
+          <t>Adisoft Technol.</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>544832</t>
+          <t>ADISOFT</t>
         </is>
       </c>
       <c r="C364" t="n">
-        <v>229.7</v>
+        <v>257</v>
       </c>
       <c r="D364" t="n">
-        <v>417.14</v>
+        <v>419.37</v>
       </c>
       <c r="E364" t="n">
-        <v>31.2</v>
+        <v>38.19</v>
       </c>
       <c r="F364" t="n">
-        <v>24.05</v>
+        <v>18.28</v>
       </c>
       <c r="G364" t="inlineStr">
         <is>
@@ -10995,25 +10995,25 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>Ravita Engineering</t>
+          <t>Sotefin Bharat</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>RAVITA</t>
+          <t>544832</t>
         </is>
       </c>
       <c r="C365" t="n">
-        <v>110.65</v>
+        <v>229.7</v>
       </c>
       <c r="D365" t="n">
-        <v>416.93</v>
+        <v>417.14</v>
       </c>
       <c r="E365" t="n">
-        <v>48.65</v>
+        <v>31.2</v>
       </c>
       <c r="F365" t="n">
-        <v>14.86</v>
+        <v>24.05</v>
       </c>
       <c r="G365" t="inlineStr">
         <is>
@@ -11024,25 +11024,25 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>Adisoft Technol.</t>
+          <t>Ravita Engineering</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>ADISOFT</t>
+          <t>RAVITA</t>
         </is>
       </c>
       <c r="C366" t="n">
-        <v>255.05</v>
+        <v>110.65</v>
       </c>
       <c r="D366" t="n">
-        <v>416.19</v>
+        <v>416.93</v>
       </c>
       <c r="E366" t="n">
-        <v>38.19</v>
+        <v>48.65</v>
       </c>
       <c r="F366" t="n">
-        <v>18.14</v>
+        <v>14.86</v>
       </c>
       <c r="G366" t="inlineStr">
         <is>
@@ -11111,25 +11111,25 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>Kwick Forensic</t>
+          <t>Arham Tech</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>544895</t>
+          <t>ARHAM</t>
         </is>
       </c>
       <c r="C369" t="n">
-        <v>191.2</v>
+        <v>188</v>
       </c>
       <c r="D369" t="n">
-        <v>409.87</v>
+        <v>410.06</v>
       </c>
       <c r="E369" t="n">
-        <v>51.41</v>
+        <v>19.8</v>
       </c>
       <c r="F369" t="n">
-        <v>30.28</v>
+        <v>33.61</v>
       </c>
       <c r="G369" t="inlineStr">
         <is>
@@ -11169,25 +11169,25 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>Arham Tech</t>
+          <t>Kwick Forensic</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>ARHAM</t>
+          <t>544895</t>
         </is>
       </c>
       <c r="C371" t="n">
-        <v>187.15</v>
+        <v>190.1</v>
       </c>
       <c r="D371" t="n">
-        <v>408.21</v>
+        <v>407.51</v>
       </c>
       <c r="E371" t="n">
-        <v>19.8</v>
+        <v>51.41</v>
       </c>
       <c r="F371" t="n">
-        <v>33.46</v>
+        <v>30.11</v>
       </c>
       <c r="G371" t="inlineStr">
         <is>
@@ -11294,16 +11294,16 @@
         </is>
       </c>
       <c r="C375" t="n">
-        <v>67.41</v>
+        <v>67.12</v>
       </c>
       <c r="D375" t="n">
-        <v>388.21</v>
+        <v>386.54</v>
       </c>
       <c r="E375" t="n">
         <v>42.71</v>
       </c>
       <c r="F375" t="n">
-        <v>17.02</v>
+        <v>16.95</v>
       </c>
       <c r="G375" t="inlineStr">
         <is>
@@ -11323,16 +11323,16 @@
         </is>
       </c>
       <c r="C376" t="n">
-        <v>402.5</v>
+        <v>401.55</v>
       </c>
       <c r="D376" t="n">
-        <v>386.81</v>
+        <v>385.9</v>
       </c>
       <c r="E376" t="n">
         <v>22.02</v>
       </c>
       <c r="F376" t="n">
-        <v>25.49</v>
+        <v>25.43</v>
       </c>
       <c r="G376" t="inlineStr">
         <is>
@@ -11352,16 +11352,16 @@
         </is>
       </c>
       <c r="C377" t="n">
-        <v>58.5</v>
+        <v>58.79</v>
       </c>
       <c r="D377" t="n">
-        <v>383.12</v>
+        <v>385.02</v>
       </c>
       <c r="E377" t="n">
         <v>21.12</v>
       </c>
       <c r="F377" t="n">
-        <v>3.73</v>
+        <v>3.74</v>
       </c>
       <c r="G377" t="inlineStr">
         <is>
@@ -11372,25 +11372,25 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>Suratwwala Busi.</t>
+          <t>TechD Cybersec.</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>SBGLP</t>
+          <t>TECHD</t>
         </is>
       </c>
       <c r="C378" t="n">
-        <v>21.9</v>
+        <v>495</v>
       </c>
       <c r="D378" t="n">
-        <v>379.79</v>
+        <v>370.24</v>
       </c>
       <c r="E378" t="n">
-        <v>30.79</v>
+        <v>40.91</v>
       </c>
       <c r="F378" t="n">
-        <v>9.06</v>
+        <v>26.36</v>
       </c>
       <c r="G378" t="inlineStr">
         <is>
@@ -11401,25 +11401,25 @@
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>TechD Cybersec.</t>
+          <t>Nisus Finance</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>TECHD</t>
+          <t>544296</t>
         </is>
       </c>
       <c r="C379" t="n">
-        <v>500</v>
+        <v>154.5</v>
       </c>
       <c r="D379" t="n">
-        <v>373.98</v>
+        <v>368.92</v>
       </c>
       <c r="E379" t="n">
-        <v>40.91</v>
+        <v>37.69</v>
       </c>
       <c r="F379" t="n">
-        <v>26.63</v>
+        <v>5.46</v>
       </c>
       <c r="G379" t="inlineStr">
         <is>
@@ -11430,25 +11430,25 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>Nisus Finance</t>
+          <t>Vishnusurya Pro.</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>544296</t>
+          <t>VISHNUINFR</t>
         </is>
       </c>
       <c r="C380" t="n">
-        <v>154.5</v>
+        <v>142</v>
       </c>
       <c r="D380" t="n">
-        <v>368.92</v>
+        <v>368.15</v>
       </c>
       <c r="E380" t="n">
-        <v>37.69</v>
+        <v>20.15</v>
       </c>
       <c r="F380" t="n">
-        <v>5.46</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="G380" t="inlineStr">
         <is>
@@ -11459,25 +11459,25 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>Vishnusurya Pro.</t>
+          <t>Suratwwala Busi.</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>VISHNUINFR</t>
+          <t>SBGLP</t>
         </is>
       </c>
       <c r="C381" t="n">
-        <v>140.25</v>
+        <v>21.01</v>
       </c>
       <c r="D381" t="n">
-        <v>363.61</v>
+        <v>364.36</v>
       </c>
       <c r="E381" t="n">
-        <v>20.15</v>
+        <v>30.79</v>
       </c>
       <c r="F381" t="n">
-        <v>8.609999999999999</v>
+        <v>8.69</v>
       </c>
       <c r="G381" t="inlineStr">
         <is>
@@ -11546,25 +11546,25 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>Patel Chem</t>
+          <t>Covance Softsol</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>544460</t>
+          <t>544361</t>
         </is>
       </c>
       <c r="C384" t="n">
-        <v>141.5</v>
+        <v>159</v>
       </c>
       <c r="D384" t="n">
-        <v>351.91</v>
+        <v>352.12</v>
       </c>
       <c r="E384" t="n">
-        <v>21.85</v>
+        <v>20.98</v>
       </c>
       <c r="F384" t="n">
-        <v>28.04</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="G384" t="inlineStr">
         <is>
@@ -11575,25 +11575,25 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>Covance Softsol</t>
+          <t>Patel Chem</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>544361</t>
+          <t>544460</t>
         </is>
       </c>
       <c r="C385" t="n">
-        <v>157</v>
+        <v>141.5</v>
       </c>
       <c r="D385" t="n">
-        <v>347.69</v>
+        <v>351.91</v>
       </c>
       <c r="E385" t="n">
-        <v>20.98</v>
+        <v>21.85</v>
       </c>
       <c r="F385" t="n">
-        <v>8.92</v>
+        <v>28.04</v>
       </c>
       <c r="G385" t="inlineStr">
         <is>
@@ -11633,25 +11633,25 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>True Colors</t>
+          <t>Ganesh Infra.</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>544531</t>
+          <t>GANESHIN</t>
         </is>
       </c>
       <c r="C387" t="n">
-        <v>138.1</v>
+        <v>78.65000000000001</v>
       </c>
       <c r="D387" t="n">
-        <v>340.48</v>
+        <v>344.26</v>
       </c>
       <c r="E387" t="n">
-        <v>25.69</v>
+        <v>18.87</v>
       </c>
       <c r="F387" t="n">
-        <v>10.89</v>
+        <v>3.76</v>
       </c>
       <c r="G387" t="inlineStr">
         <is>
@@ -11662,25 +11662,25 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>Infinity Infoway</t>
+          <t>True Colors</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>544567</t>
+          <t>544531</t>
         </is>
       </c>
       <c r="C388" t="n">
-        <v>615</v>
+        <v>138.1</v>
       </c>
       <c r="D388" t="n">
-        <v>335.36</v>
+        <v>340.48</v>
       </c>
       <c r="E388" t="n">
-        <v>35.08</v>
+        <v>25.69</v>
       </c>
       <c r="F388" t="n">
-        <v>36.34</v>
+        <v>10.89</v>
       </c>
       <c r="G388" t="inlineStr">
         <is>
@@ -11691,25 +11691,25 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>Clay Craft India</t>
+          <t>Infinity Infoway</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>CLAYCRAFT</t>
+          <t>544567</t>
         </is>
       </c>
       <c r="C389" t="n">
-        <v>162.5</v>
+        <v>615</v>
       </c>
       <c r="D389" t="n">
-        <v>334.26</v>
+        <v>335.36</v>
       </c>
       <c r="E389" t="n">
-        <v>19.96</v>
+        <v>35.08</v>
       </c>
       <c r="F389" t="n">
-        <v>12.43</v>
+        <v>36.34</v>
       </c>
       <c r="G389" t="inlineStr">
         <is>
@@ -11720,25 +11720,25 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>Encompass Design</t>
+          <t>Clay Craft India</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>ENCOMPAS</t>
+          <t>CLAYCRAFT</t>
         </is>
       </c>
       <c r="C390" t="n">
-        <v>235</v>
+        <v>162.5</v>
       </c>
       <c r="D390" t="n">
-        <v>333.32</v>
+        <v>334.26</v>
       </c>
       <c r="E390" t="n">
-        <v>25.62</v>
+        <v>19.96</v>
       </c>
       <c r="F390" t="n">
-        <v>25.61</v>
+        <v>12.43</v>
       </c>
       <c r="G390" t="inlineStr">
         <is>
@@ -11749,25 +11749,25 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>Ganesh Infra.</t>
+          <t>Encompass Design</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>GANESHIN</t>
+          <t>ENCOMPAS</t>
         </is>
       </c>
       <c r="C391" t="n">
-        <v>76.09999999999999</v>
+        <v>235</v>
       </c>
       <c r="D391" t="n">
-        <v>333.1</v>
+        <v>333.32</v>
       </c>
       <c r="E391" t="n">
-        <v>18.87</v>
+        <v>25.62</v>
       </c>
       <c r="F391" t="n">
-        <v>3.64</v>
+        <v>25.61</v>
       </c>
       <c r="G391" t="inlineStr">
         <is>
@@ -11865,25 +11865,25 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>Asarfi Hospital</t>
+          <t>SpectraA Technology</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>543943</t>
+          <t>SPECTRAA</t>
         </is>
       </c>
       <c r="C395" t="n">
-        <v>167.2</v>
+        <v>245.5</v>
       </c>
       <c r="D395" t="n">
-        <v>329</v>
+        <v>327.69</v>
       </c>
       <c r="E395" t="n">
-        <v>18.77</v>
+        <v>43.5</v>
       </c>
       <c r="F395" t="n">
-        <v>18.13</v>
+        <v>34.02</v>
       </c>
       <c r="G395" t="inlineStr">
         <is>
@@ -11894,25 +11894,25 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>SpectraA Technology</t>
+          <t>Asarfi Hospital</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>SPECTRAA</t>
+          <t>543943</t>
         </is>
       </c>
       <c r="C396" t="n">
-        <v>245.5</v>
+        <v>166.25</v>
       </c>
       <c r="D396" t="n">
-        <v>327.69</v>
+        <v>327.13</v>
       </c>
       <c r="E396" t="n">
-        <v>43.5</v>
+        <v>18.77</v>
       </c>
       <c r="F396" t="n">
-        <v>34.02</v>
+        <v>18.03</v>
       </c>
       <c r="G396" t="inlineStr">
         <is>
@@ -11932,16 +11932,16 @@
         </is>
       </c>
       <c r="C397" t="n">
-        <v>189.2</v>
+        <v>188.2</v>
       </c>
       <c r="D397" t="n">
-        <v>326.33</v>
+        <v>324.61</v>
       </c>
       <c r="E397" t="n">
         <v>23.36</v>
       </c>
       <c r="F397" t="n">
-        <v>32.05</v>
+        <v>31.88</v>
       </c>
       <c r="G397" t="inlineStr">
         <is>
@@ -12135,16 +12135,16 @@
         </is>
       </c>
       <c r="C404" t="n">
-        <v>453</v>
+        <v>454.75</v>
       </c>
       <c r="D404" t="n">
-        <v>306.82</v>
+        <v>308.01</v>
       </c>
       <c r="E404" t="n">
         <v>25.03</v>
       </c>
       <c r="F404" t="n">
-        <v>25.42</v>
+        <v>25.52</v>
       </c>
       <c r="G404" t="inlineStr">
         <is>
@@ -12164,16 +12164,16 @@
         </is>
       </c>
       <c r="C405" t="n">
-        <v>175.4</v>
+        <v>176.25</v>
       </c>
       <c r="D405" t="n">
-        <v>301.8</v>
+        <v>303.26</v>
       </c>
       <c r="E405" t="n">
         <v>19.28</v>
       </c>
       <c r="F405" t="n">
-        <v>15</v>
+        <v>15.07</v>
       </c>
       <c r="G405" t="inlineStr">
         <is>
